--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3238,6 +3238,694 @@
         <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 168.74 &lt;= Upper 170.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>230.36</v>
+      </c>
+      <c r="E66" t="n">
+        <v>232.35</v>
+      </c>
+      <c r="F66" t="n">
+        <v>232.35</v>
+      </c>
+      <c r="G66" t="n">
+        <v>222.89</v>
+      </c>
+      <c r="H66" t="n">
+        <v>219.04</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 230.36 &lt;= Upper 232.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="E67" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="F67" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="G67" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="H67" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 354.08 &lt;= Upper 373.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="E68" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="F68" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="G68" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="H68" t="n">
+        <v>316.73</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 319.97 &lt;= Upper 328.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="F69" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="G69" t="n">
+        <v>500.48</v>
+      </c>
+      <c r="H69" t="n">
+        <v>488.68</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 499.70 &lt;= Upper 516.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>616.77</v>
+      </c>
+      <c r="E70" t="n">
+        <v>619.29</v>
+      </c>
+      <c r="F70" t="n">
+        <v>619.29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>589.64</v>
+      </c>
+      <c r="H70" t="n">
+        <v>583.6</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 616.77 &lt;= Upper 619.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="E71" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="F71" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="G71" t="n">
+        <v>258.96</v>
+      </c>
+      <c r="H71" t="n">
+        <v>259.54</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 258.96 &lt;= EMA21 259.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="E72" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="F72" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="H72" t="n">
+        <v>343.38</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 340.57 &lt;= EMA21 343.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>477.57</v>
+      </c>
+      <c r="E73" t="n">
+        <v>505.22</v>
+      </c>
+      <c r="F73" t="n">
+        <v>505.22</v>
+      </c>
+      <c r="G73" t="n">
+        <v>468.28</v>
+      </c>
+      <c r="H73" t="n">
+        <v>475.5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 468.28 &lt;= EMA21 475.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="E74" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="F74" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="G74" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="H74" t="n">
+        <v>79.13</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 78.25 &lt;= Upper 84.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>174.33</v>
+      </c>
+      <c r="E75" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>177.88</v>
+      </c>
+      <c r="H75" t="n">
+        <v>171.96</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 174.33 &lt;= Upper 187.21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>357.9</v>
+      </c>
+      <c r="E76" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="F76" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="G76" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="H76" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 365.27 &lt;= EMA21 374.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>184.64</v>
+      </c>
+      <c r="E77" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="F77" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="G77" t="n">
+        <v>181.51</v>
+      </c>
+      <c r="H77" t="n">
+        <v>173.86</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 184.64 &lt;= Upper 204.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>252.09</v>
+      </c>
+      <c r="E78" t="n">
+        <v>282.59</v>
+      </c>
+      <c r="F78" t="n">
+        <v>282.59</v>
+      </c>
+      <c r="G78" t="n">
+        <v>244.99</v>
+      </c>
+      <c r="H78" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 244.99 &lt;= EMA21 252.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="E79" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="F79" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="G79" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 75.76 &lt;= Upper 80.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="E80" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G80" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="H80" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 39.59 &lt;= Upper 41.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>168.74</v>
+      </c>
+      <c r="E81" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="F81" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="G81" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>164.92</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>BELOW_BAND (Close 168.74 &lt;= Upper 170.32)</t>
         </is>
@@ -3907,7 +4595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4089,6 +4777,39 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04:53:12</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-171.28</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,61 +431,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K381"/>
+  <dimension ref="A1:K481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SMA20</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Upper_Band</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>EMA9</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>EMA21</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Vol_Ratio</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Qualifies</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Rejection_Or_Status</t>
         </is>
@@ -16664,6 +16664,4252 @@
         <v>0</v>
       </c>
       <c r="K381" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 104.47 &lt;= Upper 109.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="E382" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="F382" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="G382" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="H382" t="n">
+        <v>316.73</v>
+      </c>
+      <c r="I382" t="n">
+        <v>1</v>
+      </c>
+      <c r="J382" t="b">
+        <v>0</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 319.97 &lt;= Upper 328.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="E383" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="F383" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="G383" t="n">
+        <v>500.48</v>
+      </c>
+      <c r="H383" t="n">
+        <v>488.68</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J383" t="b">
+        <v>0</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 499.70 &lt;= Upper 516.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>230.36</v>
+      </c>
+      <c r="E384" t="n">
+        <v>232.35</v>
+      </c>
+      <c r="F384" t="n">
+        <v>232.35</v>
+      </c>
+      <c r="G384" t="n">
+        <v>222.89</v>
+      </c>
+      <c r="H384" t="n">
+        <v>219.04</v>
+      </c>
+      <c r="I384" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J384" t="b">
+        <v>0</v>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 230.36 &lt;= Upper 232.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="E385" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="F385" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="G385" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="H385" t="n">
+        <v>343.38</v>
+      </c>
+      <c r="I385" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J385" t="b">
+        <v>0</v>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 340.57 &lt;= EMA21 343.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>335.31</v>
+      </c>
+      <c r="E386" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="F386" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="G386" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="H386" t="n">
+        <v>340.59</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J386" t="b">
+        <v>0</v>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 337.35 &lt;= EMA21 340.59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="E387" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="F387" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="G387" t="n">
+        <v>258.96</v>
+      </c>
+      <c r="H387" t="n">
+        <v>259.54</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J387" t="b">
+        <v>0</v>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 258.96 &lt;= EMA21 259.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>616.77</v>
+      </c>
+      <c r="E388" t="n">
+        <v>619.29</v>
+      </c>
+      <c r="F388" t="n">
+        <v>619.29</v>
+      </c>
+      <c r="G388" t="n">
+        <v>589.64</v>
+      </c>
+      <c r="H388" t="n">
+        <v>583.6</v>
+      </c>
+      <c r="I388" t="n">
+        <v>1</v>
+      </c>
+      <c r="J388" t="b">
+        <v>0</v>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 616.77 &lt;= Upper 619.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="E389" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="F389" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="G389" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="H389" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J389" t="b">
+        <v>0</v>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 354.08 &lt;= Upper 373.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>357.9</v>
+      </c>
+      <c r="E390" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="F390" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="G390" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="H390" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="I390" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J390" t="b">
+        <v>0</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 365.27 &lt;= EMA21 374.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>158.78</v>
+      </c>
+      <c r="E391" t="n">
+        <v>158.25</v>
+      </c>
+      <c r="F391" t="n">
+        <v>158.25</v>
+      </c>
+      <c r="G391" t="n">
+        <v>150.13</v>
+      </c>
+      <c r="H391" t="n">
+        <v>147.12</v>
+      </c>
+      <c r="I391" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J391" t="b">
+        <v>0</v>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.16x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>259.23</v>
+      </c>
+      <c r="E392" t="n">
+        <v>277.39</v>
+      </c>
+      <c r="F392" t="n">
+        <v>277.39</v>
+      </c>
+      <c r="G392" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="H392" t="n">
+        <v>226.17</v>
+      </c>
+      <c r="I392" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J392" t="b">
+        <v>0</v>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 259.23 &lt;= Upper 277.39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>266.51</v>
+      </c>
+      <c r="E393" t="n">
+        <v>295.85</v>
+      </c>
+      <c r="F393" t="n">
+        <v>295.85</v>
+      </c>
+      <c r="G393" t="n">
+        <v>279.13</v>
+      </c>
+      <c r="H393" t="n">
+        <v>272.37</v>
+      </c>
+      <c r="I393" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J393" t="b">
+        <v>0</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 266.51 &lt;= Upper 295.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>477.57</v>
+      </c>
+      <c r="E394" t="n">
+        <v>505.22</v>
+      </c>
+      <c r="F394" t="n">
+        <v>505.22</v>
+      </c>
+      <c r="G394" t="n">
+        <v>468.28</v>
+      </c>
+      <c r="H394" t="n">
+        <v>475.5</v>
+      </c>
+      <c r="I394" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J394" t="b">
+        <v>0</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 468.28 &lt;= EMA21 475.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E395" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="F395" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="G395" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H395" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="I395" t="n">
+        <v>1</v>
+      </c>
+      <c r="J395" t="b">
+        <v>0</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 91.75 &lt;= EMA21 93.46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="E396" t="n">
+        <v>1020.02</v>
+      </c>
+      <c r="F396" t="n">
+        <v>1020.02</v>
+      </c>
+      <c r="G396" t="n">
+        <v>960</v>
+      </c>
+      <c r="H396" t="n">
+        <v>943.5599999999999</v>
+      </c>
+      <c r="I396" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J396" t="b">
+        <v>0</v>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 1016.59 &lt;= Upper 1020.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>168.74</v>
+      </c>
+      <c r="E397" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="F397" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="G397" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="H397" t="n">
+        <v>164.92</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J397" t="b">
+        <v>0</v>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 168.74 &lt;= Upper 170.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>258.44</v>
+      </c>
+      <c r="E398" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="F398" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="G398" t="n">
+        <v>259.01</v>
+      </c>
+      <c r="H398" t="n">
+        <v>265.44</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J398" t="b">
+        <v>0</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 259.01 &lt;= EMA21 265.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>454.71</v>
+      </c>
+      <c r="E399" t="n">
+        <v>556.71</v>
+      </c>
+      <c r="F399" t="n">
+        <v>556.71</v>
+      </c>
+      <c r="G399" t="n">
+        <v>459.14</v>
+      </c>
+      <c r="H399" t="n">
+        <v>482.28</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J399" t="b">
+        <v>0</v>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 459.14 &lt;= EMA21 482.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>307.65</v>
+      </c>
+      <c r="E400" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="F400" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="G400" t="n">
+        <v>302.31</v>
+      </c>
+      <c r="H400" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J400" t="b">
+        <v>0</v>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 302.31 &lt;= EMA21 308.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="E401" t="n">
+        <v>212.19</v>
+      </c>
+      <c r="F401" t="n">
+        <v>212.19</v>
+      </c>
+      <c r="G401" t="n">
+        <v>179.31</v>
+      </c>
+      <c r="H401" t="n">
+        <v>185.82</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J401" t="b">
+        <v>0</v>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 179.31 &lt;= EMA21 185.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>1714.88</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1878.55</v>
+      </c>
+      <c r="F402" t="n">
+        <v>1878.55</v>
+      </c>
+      <c r="G402" t="n">
+        <v>1702.66</v>
+      </c>
+      <c r="H402" t="n">
+        <v>1724.32</v>
+      </c>
+      <c r="I402" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J402" t="b">
+        <v>0</v>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1702.66 &lt;= EMA21 1724.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="E403" t="n">
+        <v>393.14</v>
+      </c>
+      <c r="F403" t="n">
+        <v>393.14</v>
+      </c>
+      <c r="G403" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="H403" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="I403" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J403" t="b">
+        <v>0</v>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 362.50 &lt;= EMA21 368.39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>223.55</v>
+      </c>
+      <c r="E404" t="n">
+        <v>252.28</v>
+      </c>
+      <c r="F404" t="n">
+        <v>252.28</v>
+      </c>
+      <c r="G404" t="n">
+        <v>219.41</v>
+      </c>
+      <c r="H404" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="I404" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J404" t="b">
+        <v>0</v>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 219.41 &lt;= EMA21 220.90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="E405" t="n">
+        <v>236.71</v>
+      </c>
+      <c r="F405" t="n">
+        <v>236.71</v>
+      </c>
+      <c r="G405" t="n">
+        <v>226.01</v>
+      </c>
+      <c r="H405" t="n">
+        <v>230.55</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1</v>
+      </c>
+      <c r="J405" t="b">
+        <v>0</v>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 226.01 &lt;= EMA21 230.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="E406" t="n">
+        <v>84.68000000000001</v>
+      </c>
+      <c r="F406" t="n">
+        <v>84.68000000000001</v>
+      </c>
+      <c r="G406" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="H406" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="I406" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J406" t="b">
+        <v>0</v>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.96 &lt;= EMA21 76.59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>1223.86</v>
+      </c>
+      <c r="E407" t="n">
+        <v>1448.39</v>
+      </c>
+      <c r="F407" t="n">
+        <v>1448.39</v>
+      </c>
+      <c r="G407" t="n">
+        <v>1252.83</v>
+      </c>
+      <c r="H407" t="n">
+        <v>1292.32</v>
+      </c>
+      <c r="I407" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J407" t="b">
+        <v>0</v>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1252.83 &lt;= EMA21 1292.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>74.02</v>
+      </c>
+      <c r="E408" t="n">
+        <v>72.64</v>
+      </c>
+      <c r="F408" t="n">
+        <v>72.64</v>
+      </c>
+      <c r="G408" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="H408" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="I408" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J408" t="b">
+        <v>0</v>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.87x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>102.84</v>
+      </c>
+      <c r="E409" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="F409" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="G409" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="H409" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="I409" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J409" t="b">
+        <v>0</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.77x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="E410" t="n">
+        <v>432</v>
+      </c>
+      <c r="F410" t="n">
+        <v>432</v>
+      </c>
+      <c r="G410" t="n">
+        <v>354.31</v>
+      </c>
+      <c r="H410" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="I410" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J410" t="b">
+        <v>0</v>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 354.31 &lt;= EMA21 364.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>138.74</v>
+      </c>
+      <c r="E411" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="F411" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="G411" t="n">
+        <v>136.59</v>
+      </c>
+      <c r="H411" t="n">
+        <v>139.71</v>
+      </c>
+      <c r="I411" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J411" t="b">
+        <v>0</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 136.59 &lt;= EMA21 139.71)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="E412" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="F412" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="G412" t="n">
+        <v>73.77</v>
+      </c>
+      <c r="H412" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J412" t="b">
+        <v>0</v>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.77 &lt;= EMA21 75.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="E413" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F413" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G413" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="H413" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J413" t="b">
+        <v>0</v>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 39.59 &lt;= Upper 41.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>524.14</v>
+      </c>
+      <c r="E414" t="n">
+        <v>521.99</v>
+      </c>
+      <c r="F414" t="n">
+        <v>521.99</v>
+      </c>
+      <c r="G414" t="n">
+        <v>480.93</v>
+      </c>
+      <c r="H414" t="n">
+        <v>464.33</v>
+      </c>
+      <c r="I414" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J414" t="b">
+        <v>1</v>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="E415" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="F415" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="G415" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="H415" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="I415" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J415" t="b">
+        <v>0</v>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.89x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>467.46</v>
+      </c>
+      <c r="E416" t="n">
+        <v>515.33</v>
+      </c>
+      <c r="F416" t="n">
+        <v>515.33</v>
+      </c>
+      <c r="G416" t="n">
+        <v>456.8</v>
+      </c>
+      <c r="H416" t="n">
+        <v>468.57</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J416" t="b">
+        <v>0</v>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 456.80 &lt;= EMA21 468.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>849.28</v>
+      </c>
+      <c r="E417" t="n">
+        <v>964.38</v>
+      </c>
+      <c r="F417" t="n">
+        <v>964.38</v>
+      </c>
+      <c r="G417" t="n">
+        <v>829.67</v>
+      </c>
+      <c r="H417" t="n">
+        <v>841.17</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J417" t="b">
+        <v>0</v>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 829.67 &lt;= EMA21 841.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>193.78</v>
+      </c>
+      <c r="E418" t="n">
+        <v>208.38</v>
+      </c>
+      <c r="F418" t="n">
+        <v>208.38</v>
+      </c>
+      <c r="G418" t="n">
+        <v>192.46</v>
+      </c>
+      <c r="H418" t="n">
+        <v>191.22</v>
+      </c>
+      <c r="I418" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J418" t="b">
+        <v>0</v>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 193.78 &lt;= Upper 208.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="E419" t="n">
+        <v>121.39</v>
+      </c>
+      <c r="F419" t="n">
+        <v>121.39</v>
+      </c>
+      <c r="G419" t="n">
+        <v>110.14</v>
+      </c>
+      <c r="H419" t="n">
+        <v>111.92</v>
+      </c>
+      <c r="I419" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J419" t="b">
+        <v>0</v>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 110.14 &lt;= EMA21 111.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>186.72</v>
+      </c>
+      <c r="E420" t="n">
+        <v>195.14</v>
+      </c>
+      <c r="F420" t="n">
+        <v>195.14</v>
+      </c>
+      <c r="G420" t="n">
+        <v>187.36</v>
+      </c>
+      <c r="H420" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="I420" t="n">
+        <v>1</v>
+      </c>
+      <c r="J420" t="b">
+        <v>0</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 186.72 &lt;= Upper 195.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>234.89</v>
+      </c>
+      <c r="E421" t="n">
+        <v>239.79</v>
+      </c>
+      <c r="F421" t="n">
+        <v>239.79</v>
+      </c>
+      <c r="G421" t="n">
+        <v>233.84</v>
+      </c>
+      <c r="H421" t="n">
+        <v>233.82</v>
+      </c>
+      <c r="I421" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J421" t="b">
+        <v>0</v>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 234.89 &lt;= Upper 239.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>141.26</v>
+      </c>
+      <c r="E422" t="n">
+        <v>149.53</v>
+      </c>
+      <c r="F422" t="n">
+        <v>149.53</v>
+      </c>
+      <c r="G422" t="n">
+        <v>138.91</v>
+      </c>
+      <c r="H422" t="n">
+        <v>131.71</v>
+      </c>
+      <c r="I422" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J422" t="b">
+        <v>0</v>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 141.26 &lt;= Upper 149.53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="E423" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="F423" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="G423" t="n">
+        <v>346.11</v>
+      </c>
+      <c r="H423" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="I423" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J423" t="b">
+        <v>0</v>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 332.70 &lt;= Upper 372.77)</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="E424" t="n">
+        <v>406.44</v>
+      </c>
+      <c r="F424" t="n">
+        <v>406.44</v>
+      </c>
+      <c r="G424" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="H424" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="I424" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J424" t="b">
+        <v>0</v>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 348.93 &lt;= EMA21 353.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="E425" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="F425" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="G425" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="H425" t="n">
+        <v>208.12</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J425" t="b">
+        <v>0</v>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 213.10 &lt;= Upper 239.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>337.18</v>
+      </c>
+      <c r="E426" t="n">
+        <v>349.02</v>
+      </c>
+      <c r="F426" t="n">
+        <v>349.02</v>
+      </c>
+      <c r="G426" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="H426" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="I426" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J426" t="b">
+        <v>0</v>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 337.18 &lt;= Upper 349.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>174.33</v>
+      </c>
+      <c r="E427" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="F427" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="G427" t="n">
+        <v>177.88</v>
+      </c>
+      <c r="H427" t="n">
+        <v>171.96</v>
+      </c>
+      <c r="I427" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J427" t="b">
+        <v>0</v>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 174.33 &lt;= Upper 187.21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>212.93</v>
+      </c>
+      <c r="E428" t="n">
+        <v>263.82</v>
+      </c>
+      <c r="F428" t="n">
+        <v>263.82</v>
+      </c>
+      <c r="G428" t="n">
+        <v>223.48</v>
+      </c>
+      <c r="H428" t="n">
+        <v>233.23</v>
+      </c>
+      <c r="I428" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J428" t="b">
+        <v>0</v>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 223.48 &lt;= EMA21 233.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="E429" t="n">
+        <v>191.99</v>
+      </c>
+      <c r="F429" t="n">
+        <v>191.99</v>
+      </c>
+      <c r="G429" t="n">
+        <v>176.87</v>
+      </c>
+      <c r="H429" t="n">
+        <v>174.57</v>
+      </c>
+      <c r="I429" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J429" t="b">
+        <v>0</v>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 169.80 &lt;= Upper 191.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>278.92</v>
+      </c>
+      <c r="E430" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="F430" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="G430" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="H430" t="n">
+        <v>289</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J430" t="b">
+        <v>0</v>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 286.95 &lt;= EMA21 289.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="E431" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="F431" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="G431" t="n">
+        <v>404.69</v>
+      </c>
+      <c r="H431" t="n">
+        <v>405.82</v>
+      </c>
+      <c r="I431" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J431" t="b">
+        <v>0</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 404.69 &lt;= EMA21 405.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>156.29</v>
+      </c>
+      <c r="E432" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="F432" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="G432" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="H432" t="n">
+        <v>159.11</v>
+      </c>
+      <c r="I432" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J432" t="b">
+        <v>0</v>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 156.29 &lt;= Upper 171.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>189.58</v>
+      </c>
+      <c r="E433" t="n">
+        <v>201.22</v>
+      </c>
+      <c r="F433" t="n">
+        <v>201.22</v>
+      </c>
+      <c r="G433" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="H433" t="n">
+        <v>168.32</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J433" t="b">
+        <v>0</v>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 189.58 &lt;= Upper 201.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>195.79</v>
+      </c>
+      <c r="E434" t="n">
+        <v>211.43</v>
+      </c>
+      <c r="F434" t="n">
+        <v>211.43</v>
+      </c>
+      <c r="G434" t="n">
+        <v>198.54</v>
+      </c>
+      <c r="H434" t="n">
+        <v>191.07</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J434" t="b">
+        <v>0</v>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 195.79 &lt;= Upper 211.43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="E435" t="n">
+        <v>269.21</v>
+      </c>
+      <c r="F435" t="n">
+        <v>269.21</v>
+      </c>
+      <c r="G435" t="n">
+        <v>248.74</v>
+      </c>
+      <c r="H435" t="n">
+        <v>241.14</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J435" t="b">
+        <v>0</v>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 247.60 &lt;= Upper 269.21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>275.09</v>
+      </c>
+      <c r="E436" t="n">
+        <v>293.78</v>
+      </c>
+      <c r="F436" t="n">
+        <v>293.78</v>
+      </c>
+      <c r="G436" t="n">
+        <v>272.63</v>
+      </c>
+      <c r="H436" t="n">
+        <v>255.94</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J436" t="b">
+        <v>0</v>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 275.09 &lt;= Upper 293.78)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="E437" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="F437" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="G437" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="H437" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="I437" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J437" t="b">
+        <v>0</v>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 99.07 &lt;= EMA21 99.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="E438" t="n">
+        <v>181.16</v>
+      </c>
+      <c r="F438" t="n">
+        <v>181.16</v>
+      </c>
+      <c r="G438" t="n">
+        <v>162.18</v>
+      </c>
+      <c r="H438" t="n">
+        <v>154.03</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J438" t="b">
+        <v>0</v>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 170.60 &lt;= Upper 181.16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>320.56</v>
+      </c>
+      <c r="E439" t="n">
+        <v>329.26</v>
+      </c>
+      <c r="F439" t="n">
+        <v>329.26</v>
+      </c>
+      <c r="G439" t="n">
+        <v>315.39</v>
+      </c>
+      <c r="H439" t="n">
+        <v>328.42</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J439" t="b">
+        <v>0</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 315.39 &lt;= EMA21 328.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>515.67</v>
+      </c>
+      <c r="E440" t="n">
+        <v>674.28</v>
+      </c>
+      <c r="F440" t="n">
+        <v>674.28</v>
+      </c>
+      <c r="G440" t="n">
+        <v>553.09</v>
+      </c>
+      <c r="H440" t="n">
+        <v>570.12</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J440" t="b">
+        <v>0</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 553.09 &lt;= EMA21 570.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="E441" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="F441" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="G441" t="n">
+        <v>315.07</v>
+      </c>
+      <c r="H441" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="I441" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J441" t="b">
+        <v>0</v>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 315.07 &lt;= EMA21 323.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>393.84</v>
+      </c>
+      <c r="E442" t="n">
+        <v>449.01</v>
+      </c>
+      <c r="F442" t="n">
+        <v>449.01</v>
+      </c>
+      <c r="G442" t="n">
+        <v>415.38</v>
+      </c>
+      <c r="H442" t="n">
+        <v>413.94</v>
+      </c>
+      <c r="I442" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J442" t="b">
+        <v>0</v>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 393.84 &lt;= Upper 449.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="E443" t="n">
+        <v>271.42</v>
+      </c>
+      <c r="F443" t="n">
+        <v>271.42</v>
+      </c>
+      <c r="G443" t="n">
+        <v>243.06</v>
+      </c>
+      <c r="H443" t="n">
+        <v>244.79</v>
+      </c>
+      <c r="I443" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J443" t="b">
+        <v>0</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 243.06 &lt;= EMA21 244.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ANSS</t>
+        </is>
+      </c>
+      <c r="J444" t="b">
+        <v>0</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>141.02</v>
+      </c>
+      <c r="E445" t="n">
+        <v>159.69</v>
+      </c>
+      <c r="F445" t="n">
+        <v>159.69</v>
+      </c>
+      <c r="G445" t="n">
+        <v>150.03</v>
+      </c>
+      <c r="H445" t="n">
+        <v>148.42</v>
+      </c>
+      <c r="I445" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J445" t="b">
+        <v>0</v>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 141.02 &lt;= Upper 159.69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>TYL</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="E446" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="F446" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="G446" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="H446" t="n">
+        <v>352.06</v>
+      </c>
+      <c r="I446" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J446" t="b">
+        <v>0</v>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 364.03 &lt;= Upper 392.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>152.25</v>
+      </c>
+      <c r="E447" t="n">
+        <v>160.78</v>
+      </c>
+      <c r="F447" t="n">
+        <v>160.78</v>
+      </c>
+      <c r="G447" t="n">
+        <v>154.28</v>
+      </c>
+      <c r="H447" t="n">
+        <v>150.53</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J447" t="b">
+        <v>0</v>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 152.25 &lt;= Upper 160.78)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>186.42</v>
+      </c>
+      <c r="E448" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="F448" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="G448" t="n">
+        <v>191.63</v>
+      </c>
+      <c r="H448" t="n">
+        <v>186.68</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J448" t="b">
+        <v>0</v>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 186.42 &lt;= Upper 204.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>62.31</v>
+      </c>
+      <c r="E449" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="F449" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="G449" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="H449" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J449" t="b">
+        <v>0</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 62.31 &lt;= Upper 66.43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E450" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F450" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="G450" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="H450" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I450" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J450" t="b">
+        <v>0</v>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 11.94 &lt;= EMA21 11.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>117.04</v>
+      </c>
+      <c r="E451" t="n">
+        <v>123.46</v>
+      </c>
+      <c r="F451" t="n">
+        <v>123.46</v>
+      </c>
+      <c r="G451" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="H451" t="n">
+        <v>109.89</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J451" t="b">
+        <v>0</v>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 117.04 &lt;= Upper 123.46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="E452" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F452" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G452" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="H452" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="I452" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J452" t="b">
+        <v>0</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 30.65 &lt;= Upper 31.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="E453" t="n">
+        <v>156.24</v>
+      </c>
+      <c r="F453" t="n">
+        <v>156.24</v>
+      </c>
+      <c r="G453" t="n">
+        <v>148.32</v>
+      </c>
+      <c r="H453" t="n">
+        <v>144.03</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J453" t="b">
+        <v>0</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 152.38 &lt;= Upper 156.24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="E454" t="n">
+        <v>423.06</v>
+      </c>
+      <c r="F454" t="n">
+        <v>423.06</v>
+      </c>
+      <c r="G454" t="n">
+        <v>394.14</v>
+      </c>
+      <c r="H454" t="n">
+        <v>396.49</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J454" t="b">
+        <v>0</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 394.14 &lt;= EMA21 396.49)</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="J455" t="b">
+        <v>0</v>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>105.22</v>
+      </c>
+      <c r="E456" t="n">
+        <v>126.45</v>
+      </c>
+      <c r="F456" t="n">
+        <v>126.45</v>
+      </c>
+      <c r="G456" t="n">
+        <v>107.53</v>
+      </c>
+      <c r="H456" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J456" t="b">
+        <v>0</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 107.53 &lt;= EMA21 110.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="J457" t="b">
+        <v>0</v>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>214.69</v>
+      </c>
+      <c r="E458" t="n">
+        <v>258.46</v>
+      </c>
+      <c r="F458" t="n">
+        <v>258.46</v>
+      </c>
+      <c r="G458" t="n">
+        <v>222.49</v>
+      </c>
+      <c r="H458" t="n">
+        <v>230.14</v>
+      </c>
+      <c r="I458" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J458" t="b">
+        <v>0</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 222.49 &lt;= EMA21 230.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="E459" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="F459" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="G459" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="H459" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J459" t="b">
+        <v>0</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.89x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E460" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="F460" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="G460" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H460" t="n">
+        <v>42</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J460" t="b">
+        <v>0</v>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 41.66 &lt;= Upper 48.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="E461" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="F461" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="G461" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="H461" t="n">
+        <v>79.13</v>
+      </c>
+      <c r="I461" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J461" t="b">
+        <v>0</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 78.25 &lt;= Upper 84.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>105.31</v>
+      </c>
+      <c r="E462" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="F462" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="G462" t="n">
+        <v>107.02</v>
+      </c>
+      <c r="H462" t="n">
+        <v>105.84</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J462" t="b">
+        <v>0</v>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 105.31 &lt;= Upper 111.37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="E463" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="F463" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="G463" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="H463" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J463" t="b">
+        <v>0</v>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 28.25 &lt;= Upper 29.37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>PARA</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G464" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H464" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I464" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J464" t="b">
+        <v>0</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1.13 &lt;= EMA21 1.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>542.4299999999999</v>
+      </c>
+      <c r="E465" t="n">
+        <v>573.6799999999999</v>
+      </c>
+      <c r="F465" t="n">
+        <v>573.6799999999999</v>
+      </c>
+      <c r="G465" t="n">
+        <v>545.02</v>
+      </c>
+      <c r="H465" t="n">
+        <v>530.99</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J465" t="b">
+        <v>0</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 542.43 &lt;= Upper 573.68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>TME</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="E466" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="F466" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="G466" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="H466" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J466" t="b">
+        <v>0</v>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 8.43 &lt;= EMA21 8.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>107.14</v>
+      </c>
+      <c r="E467" t="n">
+        <v>118.53</v>
+      </c>
+      <c r="F467" t="n">
+        <v>118.53</v>
+      </c>
+      <c r="G467" t="n">
+        <v>106.54</v>
+      </c>
+      <c r="H467" t="n">
+        <v>107.98</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J467" t="b">
+        <v>0</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 106.54 &lt;= EMA21 107.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>915.74</v>
+      </c>
+      <c r="E468" t="n">
+        <v>975.64</v>
+      </c>
+      <c r="F468" t="n">
+        <v>975.64</v>
+      </c>
+      <c r="G468" t="n">
+        <v>935.03</v>
+      </c>
+      <c r="H468" t="n">
+        <v>942.55</v>
+      </c>
+      <c r="I468" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J468" t="b">
+        <v>0</v>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 935.03 &lt;= EMA21 942.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>164.44</v>
+      </c>
+      <c r="E469" t="n">
+        <v>171.47</v>
+      </c>
+      <c r="F469" t="n">
+        <v>171.47</v>
+      </c>
+      <c r="G469" t="n">
+        <v>163.08</v>
+      </c>
+      <c r="H469" t="n">
+        <v>158.79</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J469" t="b">
+        <v>0</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 164.44 &lt;= Upper 171.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="E470" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="F470" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="G470" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="H470" t="n">
+        <v>329.48</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J470" t="b">
+        <v>0</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 323.74 &lt;= EMA21 329.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>204.45</v>
+      </c>
+      <c r="E471" t="n">
+        <v>226.37</v>
+      </c>
+      <c r="F471" t="n">
+        <v>226.37</v>
+      </c>
+      <c r="G471" t="n">
+        <v>205.68</v>
+      </c>
+      <c r="H471" t="n">
+        <v>209.64</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J471" t="b">
+        <v>0</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 205.68 &lt;= EMA21 209.64)</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="E472" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="F472" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="G472" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="H472" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J472" t="b">
+        <v>0</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 58.59 &lt;= Upper 59.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="E473" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F473" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G473" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="H473" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J473" t="b">
+        <v>0</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 12.55 &lt;= Upper 12.70)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>133.21</v>
+      </c>
+      <c r="E474" t="n">
+        <v>132.73</v>
+      </c>
+      <c r="F474" t="n">
+        <v>132.73</v>
+      </c>
+      <c r="G474" t="n">
+        <v>128.61</v>
+      </c>
+      <c r="H474" t="n">
+        <v>125.97</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J474" t="b">
+        <v>0</v>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.67x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>131.42</v>
+      </c>
+      <c r="E475" t="n">
+        <v>135.34</v>
+      </c>
+      <c r="F475" t="n">
+        <v>135.34</v>
+      </c>
+      <c r="G475" t="n">
+        <v>130.74</v>
+      </c>
+      <c r="H475" t="n">
+        <v>129.96</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J475" t="b">
+        <v>0</v>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 131.42 &lt;= Upper 135.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>BJ</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="E476" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="F476" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="G476" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="H476" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J476" t="b">
+        <v>0</v>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 92.70 &lt;= EMA21 93.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>230.69</v>
+      </c>
+      <c r="E477" t="n">
+        <v>253.75</v>
+      </c>
+      <c r="F477" t="n">
+        <v>253.75</v>
+      </c>
+      <c r="G477" t="n">
+        <v>232.18</v>
+      </c>
+      <c r="H477" t="n">
+        <v>235.58</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J477" t="b">
+        <v>0</v>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 232.18 &lt;= EMA21 235.58)</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>132.08</v>
+      </c>
+      <c r="E478" t="n">
+        <v>160.43</v>
+      </c>
+      <c r="F478" t="n">
+        <v>160.43</v>
+      </c>
+      <c r="G478" t="n">
+        <v>134.95</v>
+      </c>
+      <c r="H478" t="n">
+        <v>140.98</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J478" t="b">
+        <v>0</v>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 134.95 &lt;= EMA21 140.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="E479" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="F479" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="G479" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="H479" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J479" t="b">
+        <v>0</v>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 38.73 &lt;= EMA21 39.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="E480" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="F480" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="G480" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="H480" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="I480" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="J480" t="b">
+        <v>0</v>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 115.85 &lt;= EMA21 117.91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="E481" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="F481" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="G481" t="n">
+        <v>106.12</v>
+      </c>
+      <c r="H481" t="n">
+        <v>106.03</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J481" t="b">
+        <v>0</v>
+      </c>
+      <c r="K481" t="inlineStr">
         <is>
           <t>BELOW_BAND (Close 104.47 &lt;= Upper 109.22)</t>
         </is>
@@ -16680,41 +20926,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Signal_Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Initial_SL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Vol_Ratio</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -16870,6 +21116,37 @@
         <v>1.34</v>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>524.14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>500.55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -16890,57 +21167,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Entry_Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Entry_Price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invested</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Current_Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unrealized_PnL_Pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Hard_SL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest_High</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Days_Held</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -17002,67 +21279,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Entry_Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Exit_Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Entry_Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Exit_Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Invested</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Gross_PnL_Pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_PnL_Pct</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PnL_Amount</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Exit_Reason</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Days_Held</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -17185,57 +21462,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Order_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Expected_Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fill_Price</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slippage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -17452,27 +21729,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
@@ -17516,51 +21793,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cash_Available</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invested_Capital</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total_Equity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Realized_PnL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Win_Rate_Pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total_Trades</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Open_Positions</t>
         </is>
@@ -17827,6 +22104,39 @@
         <v>2</v>
       </c>
       <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08:03:44</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8256.299999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1572.42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-171.28</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K481"/>
+  <dimension ref="A1:K581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20912,6 +20912,4252 @@
       <c r="K481" t="inlineStr">
         <is>
           <t>BELOW_BAND (Close 104.47 &lt;= Upper 109.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="E482" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="F482" t="n">
+        <v>328.33</v>
+      </c>
+      <c r="G482" t="n">
+        <v>319.23</v>
+      </c>
+      <c r="H482" t="n">
+        <v>316.68</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J482" t="b">
+        <v>0</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 316.22 &lt;= Upper 328.33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="E483" t="n">
+        <v>515.01</v>
+      </c>
+      <c r="F483" t="n">
+        <v>515.01</v>
+      </c>
+      <c r="G483" t="n">
+        <v>499.18</v>
+      </c>
+      <c r="H483" t="n">
+        <v>489.16</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J483" t="b">
+        <v>0</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 493.95 &lt;= Upper 515.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>225.73</v>
+      </c>
+      <c r="E484" t="n">
+        <v>232.95</v>
+      </c>
+      <c r="F484" t="n">
+        <v>232.95</v>
+      </c>
+      <c r="G484" t="n">
+        <v>223.46</v>
+      </c>
+      <c r="H484" t="n">
+        <v>219.65</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J484" t="b">
+        <v>0</v>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 225.73 &lt;= Upper 232.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="E485" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="F485" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="G485" t="n">
+        <v>340.13</v>
+      </c>
+      <c r="H485" t="n">
+        <v>342.93</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J485" t="b">
+        <v>0</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 340.13 &lt;= EMA21 342.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>335.38</v>
+      </c>
+      <c r="E486" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="F486" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="G486" t="n">
+        <v>336.96</v>
+      </c>
+      <c r="H486" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J486" t="b">
+        <v>0</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 336.96 &lt;= EMA21 340.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>256.97</v>
+      </c>
+      <c r="E487" t="n">
+        <v>270.01</v>
+      </c>
+      <c r="F487" t="n">
+        <v>270.01</v>
+      </c>
+      <c r="G487" t="n">
+        <v>258.56</v>
+      </c>
+      <c r="H487" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J487" t="b">
+        <v>0</v>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 258.56 &lt;= EMA21 259.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>613.48</v>
+      </c>
+      <c r="E488" t="n">
+        <v>622.62</v>
+      </c>
+      <c r="F488" t="n">
+        <v>622.62</v>
+      </c>
+      <c r="G488" t="n">
+        <v>594.41</v>
+      </c>
+      <c r="H488" t="n">
+        <v>586.3200000000001</v>
+      </c>
+      <c r="I488" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J488" t="b">
+        <v>0</v>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 613.48 &lt;= Upper 622.62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>368.16</v>
+      </c>
+      <c r="E489" t="n">
+        <v>375.14</v>
+      </c>
+      <c r="F489" t="n">
+        <v>375.14</v>
+      </c>
+      <c r="G489" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="H489" t="n">
+        <v>353.17</v>
+      </c>
+      <c r="I489" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J489" t="b">
+        <v>0</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 368.16 &lt;= Upper 375.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="E490" t="n">
+        <v>416.56</v>
+      </c>
+      <c r="F490" t="n">
+        <v>416.56</v>
+      </c>
+      <c r="G490" t="n">
+        <v>365.93</v>
+      </c>
+      <c r="H490" t="n">
+        <v>373.62</v>
+      </c>
+      <c r="I490" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J490" t="b">
+        <v>0</v>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 365.93 &lt;= EMA21 373.62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="E491" t="n">
+        <v>160.64</v>
+      </c>
+      <c r="F491" t="n">
+        <v>160.64</v>
+      </c>
+      <c r="G491" t="n">
+        <v>152.61</v>
+      </c>
+      <c r="H491" t="n">
+        <v>148.52</v>
+      </c>
+      <c r="I491" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J491" t="b">
+        <v>1</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>249.12</v>
+      </c>
+      <c r="E492" t="n">
+        <v>280.18</v>
+      </c>
+      <c r="F492" t="n">
+        <v>280.18</v>
+      </c>
+      <c r="G492" t="n">
+        <v>247.58</v>
+      </c>
+      <c r="H492" t="n">
+        <v>228.26</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J492" t="b">
+        <v>0</v>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 249.12 &lt;= Upper 280.18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>257.26</v>
+      </c>
+      <c r="E493" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="F493" t="n">
+        <v>296.34</v>
+      </c>
+      <c r="G493" t="n">
+        <v>274.76</v>
+      </c>
+      <c r="H493" t="n">
+        <v>270.99</v>
+      </c>
+      <c r="I493" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J493" t="b">
+        <v>0</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 257.26 &lt;= Upper 296.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>505.74</v>
+      </c>
+      <c r="E494" t="n">
+        <v>509.82</v>
+      </c>
+      <c r="F494" t="n">
+        <v>509.82</v>
+      </c>
+      <c r="G494" t="n">
+        <v>475.77</v>
+      </c>
+      <c r="H494" t="n">
+        <v>478.25</v>
+      </c>
+      <c r="I494" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="J494" t="b">
+        <v>0</v>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 475.77 &lt;= EMA21 478.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="E495" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="F495" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="G495" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="H495" t="n">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="I495" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J495" t="b">
+        <v>0</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 94.30 &lt;= EMA21 94.46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>1000.26</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1020.54</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1020.54</v>
+      </c>
+      <c r="G496" t="n">
+        <v>968.05</v>
+      </c>
+      <c r="H496" t="n">
+        <v>948.71</v>
+      </c>
+      <c r="I496" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J496" t="b">
+        <v>0</v>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 1000.26 &lt;= Upper 1020.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="E497" t="n">
+        <v>172.39</v>
+      </c>
+      <c r="F497" t="n">
+        <v>172.39</v>
+      </c>
+      <c r="G497" t="n">
+        <v>167.78</v>
+      </c>
+      <c r="H497" t="n">
+        <v>165.76</v>
+      </c>
+      <c r="I497" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J497" t="b">
+        <v>1</v>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>258.92</v>
+      </c>
+      <c r="E498" t="n">
+        <v>284.02</v>
+      </c>
+      <c r="F498" t="n">
+        <v>284.02</v>
+      </c>
+      <c r="G498" t="n">
+        <v>258.99</v>
+      </c>
+      <c r="H498" t="n">
+        <v>264.84</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J498" t="b">
+        <v>0</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 258.99 &lt;= EMA21 264.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>472.79</v>
+      </c>
+      <c r="E499" t="n">
+        <v>552.86</v>
+      </c>
+      <c r="F499" t="n">
+        <v>552.86</v>
+      </c>
+      <c r="G499" t="n">
+        <v>461.87</v>
+      </c>
+      <c r="H499" t="n">
+        <v>481.42</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J499" t="b">
+        <v>0</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 461.87 &lt;= EMA21 481.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>320.42</v>
+      </c>
+      <c r="E500" t="n">
+        <v>343.41</v>
+      </c>
+      <c r="F500" t="n">
+        <v>343.41</v>
+      </c>
+      <c r="G500" t="n">
+        <v>305.94</v>
+      </c>
+      <c r="H500" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="I500" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J500" t="b">
+        <v>0</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 305.94 &lt;= EMA21 309.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>188.98</v>
+      </c>
+      <c r="E501" t="n">
+        <v>211.92</v>
+      </c>
+      <c r="F501" t="n">
+        <v>211.92</v>
+      </c>
+      <c r="G501" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="H501" t="n">
+        <v>186.11</v>
+      </c>
+      <c r="I501" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J501" t="b">
+        <v>0</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 181.25 &lt;= EMA21 186.11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>1764.85</v>
+      </c>
+      <c r="E502" t="n">
+        <v>1879.89</v>
+      </c>
+      <c r="F502" t="n">
+        <v>1879.89</v>
+      </c>
+      <c r="G502" t="n">
+        <v>1715.1</v>
+      </c>
+      <c r="H502" t="n">
+        <v>1728.01</v>
+      </c>
+      <c r="I502" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J502" t="b">
+        <v>0</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1715.10 &lt;= EMA21 1728.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="E503" t="n">
+        <v>391.82</v>
+      </c>
+      <c r="F503" t="n">
+        <v>391.82</v>
+      </c>
+      <c r="G503" t="n">
+        <v>362.64</v>
+      </c>
+      <c r="H503" t="n">
+        <v>367.92</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J503" t="b">
+        <v>0</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 362.64 &lt;= EMA21 367.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>225.41</v>
+      </c>
+      <c r="E504" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="F504" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="G504" t="n">
+        <v>220.61</v>
+      </c>
+      <c r="H504" t="n">
+        <v>221.31</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J504" t="b">
+        <v>0</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 220.61 &lt;= EMA21 221.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>223.87</v>
+      </c>
+      <c r="E505" t="n">
+        <v>235.96</v>
+      </c>
+      <c r="F505" t="n">
+        <v>235.96</v>
+      </c>
+      <c r="G505" t="n">
+        <v>225.58</v>
+      </c>
+      <c r="H505" t="n">
+        <v>229.94</v>
+      </c>
+      <c r="I505" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J505" t="b">
+        <v>0</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 225.58 &lt;= EMA21 229.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="E506" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="F506" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="G506" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="H506" t="n">
+        <v>76.09</v>
+      </c>
+      <c r="I506" t="n">
+        <v>2</v>
+      </c>
+      <c r="J506" t="b">
+        <v>0</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.38 &lt;= EMA21 76.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>1218.5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>1442.55</v>
+      </c>
+      <c r="F507" t="n">
+        <v>1442.55</v>
+      </c>
+      <c r="G507" t="n">
+        <v>1245.96</v>
+      </c>
+      <c r="H507" t="n">
+        <v>1285.61</v>
+      </c>
+      <c r="I507" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J507" t="b">
+        <v>0</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1245.96 &lt;= EMA21 1285.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>75.38</v>
+      </c>
+      <c r="E508" t="n">
+        <v>74</v>
+      </c>
+      <c r="F508" t="n">
+        <v>74</v>
+      </c>
+      <c r="G508" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="H508" t="n">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="I508" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J508" t="b">
+        <v>0</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.23x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="E509" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="F509" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="G509" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="H509" t="n">
+        <v>97.33</v>
+      </c>
+      <c r="I509" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J509" t="b">
+        <v>1</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="E510" t="n">
+        <v>432.17</v>
+      </c>
+      <c r="F510" t="n">
+        <v>432.17</v>
+      </c>
+      <c r="G510" t="n">
+        <v>357.86</v>
+      </c>
+      <c r="H510" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="I510" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J510" t="b">
+        <v>0</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 357.86 &lt;= EMA21 365.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>141.09</v>
+      </c>
+      <c r="E511" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="F511" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="G511" t="n">
+        <v>137.49</v>
+      </c>
+      <c r="H511" t="n">
+        <v>139.84</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J511" t="b">
+        <v>0</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 137.49 &lt;= EMA21 139.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="E512" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="F512" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="G512" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="H512" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="I512" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J512" t="b">
+        <v>0</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.69 &lt;= EMA21 75.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="E513" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F513" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G513" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="H513" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J513" t="b">
+        <v>0</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 40.26 &lt;= Upper 41.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>533.88</v>
+      </c>
+      <c r="E514" t="n">
+        <v>533.27</v>
+      </c>
+      <c r="F514" t="n">
+        <v>533.27</v>
+      </c>
+      <c r="G514" t="n">
+        <v>491.52</v>
+      </c>
+      <c r="H514" t="n">
+        <v>470.66</v>
+      </c>
+      <c r="I514" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J514" t="b">
+        <v>0</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.78x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="E515" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="F515" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="G515" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="H515" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="I515" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J515" t="b">
+        <v>0</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 31.17 &lt;= Upper 32.49)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>477.3</v>
+      </c>
+      <c r="E516" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="F516" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="G516" t="n">
+        <v>460.9</v>
+      </c>
+      <c r="H516" t="n">
+        <v>469.37</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J516" t="b">
+        <v>0</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 460.90 &lt;= EMA21 469.37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>904.38</v>
+      </c>
+      <c r="E517" t="n">
+        <v>968.91</v>
+      </c>
+      <c r="F517" t="n">
+        <v>968.91</v>
+      </c>
+      <c r="G517" t="n">
+        <v>844.61</v>
+      </c>
+      <c r="H517" t="n">
+        <v>846.92</v>
+      </c>
+      <c r="I517" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J517" t="b">
+        <v>0</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 844.61 &lt;= EMA21 846.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>194.96</v>
+      </c>
+      <c r="E518" t="n">
+        <v>208.48</v>
+      </c>
+      <c r="F518" t="n">
+        <v>208.48</v>
+      </c>
+      <c r="G518" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="H518" t="n">
+        <v>191.56</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J518" t="b">
+        <v>0</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 194.96 &lt;= Upper 208.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>109.17</v>
+      </c>
+      <c r="E519" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="F519" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="G519" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="H519" t="n">
+        <v>111.67</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J519" t="b">
+        <v>0</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 109.95 &lt;= EMA21 111.67)</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>179.03</v>
+      </c>
+      <c r="E520" t="n">
+        <v>195.12</v>
+      </c>
+      <c r="F520" t="n">
+        <v>195.12</v>
+      </c>
+      <c r="G520" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="H520" t="n">
+        <v>181.26</v>
+      </c>
+      <c r="I520" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J520" t="b">
+        <v>0</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 179.03 &lt;= Upper 195.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>232.09</v>
+      </c>
+      <c r="E521" t="n">
+        <v>239.58</v>
+      </c>
+      <c r="F521" t="n">
+        <v>239.58</v>
+      </c>
+      <c r="G521" t="n">
+        <v>233.49</v>
+      </c>
+      <c r="H521" t="n">
+        <v>233.67</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J521" t="b">
+        <v>0</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 233.49 &lt;= EMA21 233.67)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>134.21</v>
+      </c>
+      <c r="E522" t="n">
+        <v>149.79</v>
+      </c>
+      <c r="F522" t="n">
+        <v>149.79</v>
+      </c>
+      <c r="G522" t="n">
+        <v>137.97</v>
+      </c>
+      <c r="H522" t="n">
+        <v>131.94</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J522" t="b">
+        <v>0</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 134.21 &lt;= Upper 149.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>318.93</v>
+      </c>
+      <c r="E523" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="F523" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="G523" t="n">
+        <v>340.67</v>
+      </c>
+      <c r="H523" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J523" t="b">
+        <v>0</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 340.67 &lt;= EMA21 340.68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>336.98</v>
+      </c>
+      <c r="E524" t="n">
+        <v>404.41</v>
+      </c>
+      <c r="F524" t="n">
+        <v>404.41</v>
+      </c>
+      <c r="G524" t="n">
+        <v>346.54</v>
+      </c>
+      <c r="H524" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J524" t="b">
+        <v>0</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 346.54 &lt;= EMA21 352.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>210.02</v>
+      </c>
+      <c r="E525" t="n">
+        <v>237.81</v>
+      </c>
+      <c r="F525" t="n">
+        <v>237.81</v>
+      </c>
+      <c r="G525" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="H525" t="n">
+        <v>208.29</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J525" t="b">
+        <v>0</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 210.02 &lt;= Upper 237.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="E526" t="n">
+        <v>349.12</v>
+      </c>
+      <c r="F526" t="n">
+        <v>349.12</v>
+      </c>
+      <c r="G526" t="n">
+        <v>330.96</v>
+      </c>
+      <c r="H526" t="n">
+        <v>323.62</v>
+      </c>
+      <c r="I526" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" t="b">
+        <v>0</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 335.50 &lt;= Upper 349.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="E527" t="n">
+        <v>187.36</v>
+      </c>
+      <c r="F527" t="n">
+        <v>187.36</v>
+      </c>
+      <c r="G527" t="n">
+        <v>176.36</v>
+      </c>
+      <c r="H527" t="n">
+        <v>171.81</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J527" t="b">
+        <v>0</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 170.30 &lt;= Upper 187.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>210.23</v>
+      </c>
+      <c r="E528" t="n">
+        <v>260.73</v>
+      </c>
+      <c r="F528" t="n">
+        <v>260.73</v>
+      </c>
+      <c r="G528" t="n">
+        <v>220.83</v>
+      </c>
+      <c r="H528" t="n">
+        <v>231.14</v>
+      </c>
+      <c r="I528" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J528" t="b">
+        <v>0</v>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 220.83 &lt;= EMA21 231.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>161.94</v>
+      </c>
+      <c r="E529" t="n">
+        <v>193.48</v>
+      </c>
+      <c r="F529" t="n">
+        <v>193.48</v>
+      </c>
+      <c r="G529" t="n">
+        <v>173.88</v>
+      </c>
+      <c r="H529" t="n">
+        <v>173.42</v>
+      </c>
+      <c r="I529" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J529" t="b">
+        <v>0</v>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 161.94 &lt;= Upper 193.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>284.3</v>
+      </c>
+      <c r="E530" t="n">
+        <v>326</v>
+      </c>
+      <c r="F530" t="n">
+        <v>326</v>
+      </c>
+      <c r="G530" t="n">
+        <v>286.42</v>
+      </c>
+      <c r="H530" t="n">
+        <v>288.57</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J530" t="b">
+        <v>0</v>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 286.42 &lt;= EMA21 288.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>356</v>
+      </c>
+      <c r="E531" t="n">
+        <v>485.93</v>
+      </c>
+      <c r="F531" t="n">
+        <v>485.93</v>
+      </c>
+      <c r="G531" t="n">
+        <v>394.95</v>
+      </c>
+      <c r="H531" t="n">
+        <v>401.29</v>
+      </c>
+      <c r="I531" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J531" t="b">
+        <v>0</v>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 394.95 &lt;= EMA21 401.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>157.47</v>
+      </c>
+      <c r="E532" t="n">
+        <v>171.12</v>
+      </c>
+      <c r="F532" t="n">
+        <v>171.12</v>
+      </c>
+      <c r="G532" t="n">
+        <v>158.85</v>
+      </c>
+      <c r="H532" t="n">
+        <v>158.96</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J532" t="b">
+        <v>0</v>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 158.85 &lt;= EMA21 158.96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>176.42</v>
+      </c>
+      <c r="E533" t="n">
+        <v>200.58</v>
+      </c>
+      <c r="F533" t="n">
+        <v>200.58</v>
+      </c>
+      <c r="G533" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="H533" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J533" t="b">
+        <v>0</v>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 176.42 &lt;= Upper 200.58)</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>186.28</v>
+      </c>
+      <c r="E534" t="n">
+        <v>211.25</v>
+      </c>
+      <c r="F534" t="n">
+        <v>211.25</v>
+      </c>
+      <c r="G534" t="n">
+        <v>196.09</v>
+      </c>
+      <c r="H534" t="n">
+        <v>190.64</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J534" t="b">
+        <v>0</v>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 186.28 &lt;= Upper 211.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>240.42</v>
+      </c>
+      <c r="E535" t="n">
+        <v>268.53</v>
+      </c>
+      <c r="F535" t="n">
+        <v>268.53</v>
+      </c>
+      <c r="G535" t="n">
+        <v>247.08</v>
+      </c>
+      <c r="H535" t="n">
+        <v>241.08</v>
+      </c>
+      <c r="I535" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J535" t="b">
+        <v>0</v>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 240.42 &lt;= Upper 268.53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>264.84</v>
+      </c>
+      <c r="E536" t="n">
+        <v>293.84</v>
+      </c>
+      <c r="F536" t="n">
+        <v>293.84</v>
+      </c>
+      <c r="G536" t="n">
+        <v>271.07</v>
+      </c>
+      <c r="H536" t="n">
+        <v>256.75</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J536" t="b">
+        <v>0</v>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 264.84 &lt;= Upper 293.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="E537" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="F537" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="G537" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="H537" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J537" t="b">
+        <v>0</v>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 98.55 &lt;= EMA21 99.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="E538" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="F538" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="G538" t="n">
+        <v>163.27</v>
+      </c>
+      <c r="H538" t="n">
+        <v>155.26</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J538" t="b">
+        <v>0</v>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 167.60 &lt;= Upper 182.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>312.01</v>
+      </c>
+      <c r="E539" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="F539" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="G539" t="n">
+        <v>314.71</v>
+      </c>
+      <c r="H539" t="n">
+        <v>326.93</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J539" t="b">
+        <v>0</v>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 314.71 &lt;= EMA21 326.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>505.43</v>
+      </c>
+      <c r="E540" t="n">
+        <v>678.45</v>
+      </c>
+      <c r="F540" t="n">
+        <v>678.45</v>
+      </c>
+      <c r="G540" t="n">
+        <v>543.5599999999999</v>
+      </c>
+      <c r="H540" t="n">
+        <v>564.23</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J540" t="b">
+        <v>0</v>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 543.56 &lt;= EMA21 564.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>284.11</v>
+      </c>
+      <c r="E541" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="F541" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="G541" t="n">
+        <v>308.87</v>
+      </c>
+      <c r="H541" t="n">
+        <v>319.92</v>
+      </c>
+      <c r="I541" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J541" t="b">
+        <v>0</v>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 308.87 &lt;= EMA21 319.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>392.03</v>
+      </c>
+      <c r="E542" t="n">
+        <v>449.41</v>
+      </c>
+      <c r="F542" t="n">
+        <v>449.41</v>
+      </c>
+      <c r="G542" t="n">
+        <v>410.71</v>
+      </c>
+      <c r="H542" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="I542" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J542" t="b">
+        <v>0</v>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 410.71 &lt;= EMA21 411.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>212.21</v>
+      </c>
+      <c r="E543" t="n">
+        <v>275.03</v>
+      </c>
+      <c r="F543" t="n">
+        <v>275.03</v>
+      </c>
+      <c r="G543" t="n">
+        <v>236.89</v>
+      </c>
+      <c r="H543" t="n">
+        <v>241.83</v>
+      </c>
+      <c r="I543" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J543" t="b">
+        <v>0</v>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 236.89 &lt;= EMA21 241.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>ANSS</t>
+        </is>
+      </c>
+      <c r="J544" t="b">
+        <v>0</v>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>133.26</v>
+      </c>
+      <c r="E545" t="n">
+        <v>162.12</v>
+      </c>
+      <c r="F545" t="n">
+        <v>162.12</v>
+      </c>
+      <c r="G545" t="n">
+        <v>146.68</v>
+      </c>
+      <c r="H545" t="n">
+        <v>147.05</v>
+      </c>
+      <c r="I545" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J545" t="b">
+        <v>0</v>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 146.68 &lt;= EMA21 147.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>TYL</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="E546" t="n">
+        <v>391.79</v>
+      </c>
+      <c r="F546" t="n">
+        <v>391.79</v>
+      </c>
+      <c r="G546" t="n">
+        <v>362.98</v>
+      </c>
+      <c r="H546" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="I546" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J546" t="b">
+        <v>0</v>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 347.82 &lt;= Upper 391.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>143.53</v>
+      </c>
+      <c r="E547" t="n">
+        <v>161.02</v>
+      </c>
+      <c r="F547" t="n">
+        <v>161.02</v>
+      </c>
+      <c r="G547" t="n">
+        <v>152.13</v>
+      </c>
+      <c r="H547" t="n">
+        <v>149.89</v>
+      </c>
+      <c r="I547" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J547" t="b">
+        <v>0</v>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 143.53 &lt;= Upper 161.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>172.59</v>
+      </c>
+      <c r="E548" t="n">
+        <v>205.53</v>
+      </c>
+      <c r="F548" t="n">
+        <v>205.53</v>
+      </c>
+      <c r="G548" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="H548" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="I548" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J548" t="b">
+        <v>0</v>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 172.59 &lt;= Upper 205.53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="E549" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="F549" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="G549" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="H549" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J549" t="b">
+        <v>0</v>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 59.92 &lt;= Upper 66.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="E550" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F550" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="G550" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H550" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="I550" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J550" t="b">
+        <v>0</v>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 11.78 &lt;= EMA21 11.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>115.31</v>
+      </c>
+      <c r="E551" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="F551" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="G551" t="n">
+        <v>115.14</v>
+      </c>
+      <c r="H551" t="n">
+        <v>110.39</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J551" t="b">
+        <v>0</v>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 115.31 &lt;= Upper 123.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="E552" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="F552" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="G552" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="H552" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J552" t="b">
+        <v>0</v>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 29.81 &lt;= Upper 31.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>144.48</v>
+      </c>
+      <c r="E553" t="n">
+        <v>156.47</v>
+      </c>
+      <c r="F553" t="n">
+        <v>156.47</v>
+      </c>
+      <c r="G553" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="H553" t="n">
+        <v>144.07</v>
+      </c>
+      <c r="I553" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J553" t="b">
+        <v>0</v>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 144.48 &lt;= Upper 156.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>389.62</v>
+      </c>
+      <c r="E554" t="n">
+        <v>421.51</v>
+      </c>
+      <c r="F554" t="n">
+        <v>421.51</v>
+      </c>
+      <c r="G554" t="n">
+        <v>393.23</v>
+      </c>
+      <c r="H554" t="n">
+        <v>395.87</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J554" t="b">
+        <v>0</v>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 393.23 &lt;= EMA21 395.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="J555" t="b">
+        <v>0</v>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>105.61</v>
+      </c>
+      <c r="E556" t="n">
+        <v>125.94</v>
+      </c>
+      <c r="F556" t="n">
+        <v>125.94</v>
+      </c>
+      <c r="G556" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="H556" t="n">
+        <v>110.44</v>
+      </c>
+      <c r="I556" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J556" t="b">
+        <v>0</v>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 107.15 &lt;= EMA21 110.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="J557" t="b">
+        <v>0</v>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>213.29</v>
+      </c>
+      <c r="E558" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="F558" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="G558" t="n">
+        <v>220.65</v>
+      </c>
+      <c r="H558" t="n">
+        <v>228.61</v>
+      </c>
+      <c r="I558" t="n">
+        <v>1</v>
+      </c>
+      <c r="J558" t="b">
+        <v>0</v>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 220.65 &lt;= EMA21 228.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="E559" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="F559" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="G559" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="H559" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="I559" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J559" t="b">
+        <v>0</v>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.24x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="E560" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="F560" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="G560" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="H560" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="I560" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J560" t="b">
+        <v>0</v>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 42.75 &lt;= Upper 48.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="E561" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="F561" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="G561" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="H561" t="n">
+        <v>78.91</v>
+      </c>
+      <c r="I561" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J561" t="b">
+        <v>0</v>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 76.77 &lt;= Upper 84.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>105.06</v>
+      </c>
+      <c r="E562" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="F562" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="G562" t="n">
+        <v>106.63</v>
+      </c>
+      <c r="H562" t="n">
+        <v>105.77</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J562" t="b">
+        <v>0</v>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 105.06 &lt;= Upper 111.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="E563" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="F563" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="G563" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="H563" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J563" t="b">
+        <v>0</v>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 28.12 &lt;= Upper 29.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>PARA</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E564" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F564" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G564" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H564" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J564" t="b">
+        <v>0</v>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1.11 &lt;= EMA21 1.33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>528.64</v>
+      </c>
+      <c r="E565" t="n">
+        <v>573.75</v>
+      </c>
+      <c r="F565" t="n">
+        <v>573.75</v>
+      </c>
+      <c r="G565" t="n">
+        <v>541.74</v>
+      </c>
+      <c r="H565" t="n">
+        <v>530.77</v>
+      </c>
+      <c r="I565" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J565" t="b">
+        <v>0</v>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 528.64 &lt;= Upper 573.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>TME</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="E566" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="F566" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="G566" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H566" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J566" t="b">
+        <v>0</v>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 8.36 &lt;= EMA21 8.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="E567" t="n">
+        <v>118.13</v>
+      </c>
+      <c r="F567" t="n">
+        <v>118.13</v>
+      </c>
+      <c r="G567" t="n">
+        <v>106.44</v>
+      </c>
+      <c r="H567" t="n">
+        <v>107.81</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J567" t="b">
+        <v>0</v>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 106.44 &lt;= EMA21 107.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>910.1799999999999</v>
+      </c>
+      <c r="E568" t="n">
+        <v>977.8099999999999</v>
+      </c>
+      <c r="F568" t="n">
+        <v>977.8099999999999</v>
+      </c>
+      <c r="G568" t="n">
+        <v>930.0599999999999</v>
+      </c>
+      <c r="H568" t="n">
+        <v>939.61</v>
+      </c>
+      <c r="I568" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J568" t="b">
+        <v>0</v>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 930.06 &lt;= EMA21 939.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>162.71</v>
+      </c>
+      <c r="E569" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="F569" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="G569" t="n">
+        <v>163</v>
+      </c>
+      <c r="H569" t="n">
+        <v>159.15</v>
+      </c>
+      <c r="I569" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J569" t="b">
+        <v>0</v>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 162.71 &lt;= Upper 171.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="E570" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="F570" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="G570" t="n">
+        <v>321.73</v>
+      </c>
+      <c r="H570" t="n">
+        <v>328.04</v>
+      </c>
+      <c r="I570" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J570" t="b">
+        <v>0</v>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 321.73 &lt;= EMA21 328.04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="E571" t="n">
+        <v>225.99</v>
+      </c>
+      <c r="F571" t="n">
+        <v>225.99</v>
+      </c>
+      <c r="G571" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="H571" t="n">
+        <v>208.84</v>
+      </c>
+      <c r="I571" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J571" t="b">
+        <v>0</v>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 204.70 &lt;= EMA21 208.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E572" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="F572" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="G572" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="H572" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="I572" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J572" t="b">
+        <v>0</v>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 57.20 &lt;= Upper 59.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="E573" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F573" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G573" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="H573" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I573" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J573" t="b">
+        <v>0</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 12.39 &lt;= EMA21 12.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>127.87</v>
+      </c>
+      <c r="E574" t="n">
+        <v>133.09</v>
+      </c>
+      <c r="F574" t="n">
+        <v>133.09</v>
+      </c>
+      <c r="G574" t="n">
+        <v>128.46</v>
+      </c>
+      <c r="H574" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J574" t="b">
+        <v>0</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 127.87 &lt;= Upper 133.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>124.04</v>
+      </c>
+      <c r="E575" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="F575" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="G575" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="H575" t="n">
+        <v>129.42</v>
+      </c>
+      <c r="I575" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J575" t="b">
+        <v>0</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 129.40 &lt;= EMA21 129.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>BJ</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="E576" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="F576" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="G576" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="H576" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J576" t="b">
+        <v>0</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 92.13 &lt;= EMA21 92.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>229.31</v>
+      </c>
+      <c r="E577" t="n">
+        <v>250.62</v>
+      </c>
+      <c r="F577" t="n">
+        <v>250.62</v>
+      </c>
+      <c r="G577" t="n">
+        <v>231.61</v>
+      </c>
+      <c r="H577" t="n">
+        <v>235.01</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J577" t="b">
+        <v>0</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 231.61 &lt;= EMA21 235.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>128.92</v>
+      </c>
+      <c r="E578" t="n">
+        <v>158.28</v>
+      </c>
+      <c r="F578" t="n">
+        <v>158.28</v>
+      </c>
+      <c r="G578" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="H578" t="n">
+        <v>139.88</v>
+      </c>
+      <c r="I578" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J578" t="b">
+        <v>0</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 133.75 &lt;= EMA21 139.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E579" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F579" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="G579" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="H579" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="I579" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J579" t="b">
+        <v>0</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 38.60 &lt;= EMA21 39.37)</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>103.19</v>
+      </c>
+      <c r="E580" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="F580" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="G580" t="n">
+        <v>113.32</v>
+      </c>
+      <c r="H580" t="n">
+        <v>116.57</v>
+      </c>
+      <c r="I580" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J580" t="b">
+        <v>0</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 113.32 &lt;= EMA21 116.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>102.01</v>
+      </c>
+      <c r="E581" t="n">
+        <v>109.61</v>
+      </c>
+      <c r="F581" t="n">
+        <v>109.61</v>
+      </c>
+      <c r="G581" t="n">
+        <v>105.29</v>
+      </c>
+      <c r="H581" t="n">
+        <v>105.66</v>
+      </c>
+      <c r="I581" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J581" t="b">
+        <v>0</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 105.29 &lt;= EMA21 105.66)</t>
         </is>
       </c>
     </row>
@@ -20926,7 +25172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21147,6 +25393,99 @@
         <v>1.34</v>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="E8" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>166.26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -21163,7 +25502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21259,6 +25598,129 @@
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1914.99</v>
+      </c>
+      <c r="F3" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>166.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1950.24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1977.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -21458,7 +25920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21709,6 +26171,153 @@
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:53:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>83C0264FA2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="G6" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:53:26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14C96CCE2E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:53:26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BCEF2D0EB1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Entry Breakout</t>
         </is>
@@ -21793,7 +26402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22140,6 +26749,39 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>04:53:28</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2413.74</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7414.98</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-171.28</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K581"/>
+  <dimension ref="A1:K681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25158,6 +25158,4252 @@
       <c r="K581" t="inlineStr">
         <is>
           <t>EMA_BEARISH (EMA9 105.29 &lt;= EMA21 105.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>315.34</v>
+      </c>
+      <c r="E582" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="F582" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="G582" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="H582" t="n">
+        <v>316.56</v>
+      </c>
+      <c r="I582" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J582" t="b">
+        <v>0</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 315.34 &lt;= Upper 328.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>491.65</v>
+      </c>
+      <c r="E583" t="n">
+        <v>514.12</v>
+      </c>
+      <c r="F583" t="n">
+        <v>514.12</v>
+      </c>
+      <c r="G583" t="n">
+        <v>497.67</v>
+      </c>
+      <c r="H583" t="n">
+        <v>489.39</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J583" t="b">
+        <v>0</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 491.65 &lt;= Upper 514.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>223.67</v>
+      </c>
+      <c r="E584" t="n">
+        <v>233.25</v>
+      </c>
+      <c r="F584" t="n">
+        <v>233.25</v>
+      </c>
+      <c r="G584" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="H584" t="n">
+        <v>220.01</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J584" t="b">
+        <v>0</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 223.67 &lt;= Upper 233.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>330.65</v>
+      </c>
+      <c r="E585" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="F585" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="G585" t="n">
+        <v>338.24</v>
+      </c>
+      <c r="H585" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="I585" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J585" t="b">
+        <v>0</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 338.24 &lt;= EMA21 341.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="E586" t="n">
+        <v>347.7</v>
+      </c>
+      <c r="F586" t="n">
+        <v>347.7</v>
+      </c>
+      <c r="G586" t="n">
+        <v>335.24</v>
+      </c>
+      <c r="H586" t="n">
+        <v>339.05</v>
+      </c>
+      <c r="I586" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J586" t="b">
+        <v>0</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 335.24 &lt;= EMA21 339.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>252.4</v>
+      </c>
+      <c r="E587" t="n">
+        <v>268.18</v>
+      </c>
+      <c r="F587" t="n">
+        <v>268.18</v>
+      </c>
+      <c r="G587" t="n">
+        <v>257.33</v>
+      </c>
+      <c r="H587" t="n">
+        <v>258.68</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J587" t="b">
+        <v>0</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 257.33 &lt;= EMA21 258.68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>653.6900000000001</v>
+      </c>
+      <c r="E588" t="n">
+        <v>636.16</v>
+      </c>
+      <c r="F588" t="n">
+        <v>636.16</v>
+      </c>
+      <c r="G588" t="n">
+        <v>606.27</v>
+      </c>
+      <c r="H588" t="n">
+        <v>592.4400000000001</v>
+      </c>
+      <c r="I588" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J588" t="b">
+        <v>1</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>367.81</v>
+      </c>
+      <c r="E589" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="F589" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="G589" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="H589" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J589" t="b">
+        <v>0</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 367.81 &lt;= Upper 376.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>364.38</v>
+      </c>
+      <c r="E590" t="n">
+        <v>409.51</v>
+      </c>
+      <c r="F590" t="n">
+        <v>409.51</v>
+      </c>
+      <c r="G590" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="H590" t="n">
+        <v>372.78</v>
+      </c>
+      <c r="I590" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J590" t="b">
+        <v>0</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 365.62 &lt;= EMA21 372.78)</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>161.63</v>
+      </c>
+      <c r="E591" t="n">
+        <v>162.63</v>
+      </c>
+      <c r="F591" t="n">
+        <v>162.63</v>
+      </c>
+      <c r="G591" t="n">
+        <v>154.41</v>
+      </c>
+      <c r="H591" t="n">
+        <v>149.71</v>
+      </c>
+      <c r="I591" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J591" t="b">
+        <v>0</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 161.63 &lt;= Upper 162.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>244.16</v>
+      </c>
+      <c r="E592" t="n">
+        <v>281.85</v>
+      </c>
+      <c r="F592" t="n">
+        <v>281.85</v>
+      </c>
+      <c r="G592" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="H592" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="I592" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J592" t="b">
+        <v>0</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 244.16 &lt;= Upper 281.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>254.86</v>
+      </c>
+      <c r="E593" t="n">
+        <v>296.99</v>
+      </c>
+      <c r="F593" t="n">
+        <v>296.99</v>
+      </c>
+      <c r="G593" t="n">
+        <v>270.78</v>
+      </c>
+      <c r="H593" t="n">
+        <v>269.53</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J593" t="b">
+        <v>0</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 254.86 &lt;= Upper 296.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>521.09</v>
+      </c>
+      <c r="E594" t="n">
+        <v>517.58</v>
+      </c>
+      <c r="F594" t="n">
+        <v>517.58</v>
+      </c>
+      <c r="G594" t="n">
+        <v>484.84</v>
+      </c>
+      <c r="H594" t="n">
+        <v>482.15</v>
+      </c>
+      <c r="I594" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J594" t="b">
+        <v>0</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.22x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="E595" t="n">
+        <v>107.81</v>
+      </c>
+      <c r="F595" t="n">
+        <v>107.81</v>
+      </c>
+      <c r="G595" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="H595" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="I595" t="n">
+        <v>1</v>
+      </c>
+      <c r="J595" t="b">
+        <v>0</v>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 106.24 &lt;= Upper 107.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>1027.77</v>
+      </c>
+      <c r="E596" t="n">
+        <v>1025.53</v>
+      </c>
+      <c r="F596" t="n">
+        <v>1025.53</v>
+      </c>
+      <c r="G596" t="n">
+        <v>980</v>
+      </c>
+      <c r="H596" t="n">
+        <v>955.9</v>
+      </c>
+      <c r="I596" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J596" t="b">
+        <v>0</v>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.86x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="E597" t="n">
+        <v>174.73</v>
+      </c>
+      <c r="F597" t="n">
+        <v>174.73</v>
+      </c>
+      <c r="G597" t="n">
+        <v>169.51</v>
+      </c>
+      <c r="H597" t="n">
+        <v>166.72</v>
+      </c>
+      <c r="I597" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J597" t="b">
+        <v>1</v>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>261.59</v>
+      </c>
+      <c r="E598" t="n">
+        <v>281.54</v>
+      </c>
+      <c r="F598" t="n">
+        <v>281.54</v>
+      </c>
+      <c r="G598" t="n">
+        <v>259.51</v>
+      </c>
+      <c r="H598" t="n">
+        <v>264.55</v>
+      </c>
+      <c r="I598" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J598" t="b">
+        <v>0</v>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 259.51 &lt;= EMA21 264.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>468.85</v>
+      </c>
+      <c r="E599" t="n">
+        <v>547.95</v>
+      </c>
+      <c r="F599" t="n">
+        <v>547.95</v>
+      </c>
+      <c r="G599" t="n">
+        <v>463.27</v>
+      </c>
+      <c r="H599" t="n">
+        <v>480.28</v>
+      </c>
+      <c r="I599" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J599" t="b">
+        <v>0</v>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 463.27 &lt;= EMA21 480.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>315.84</v>
+      </c>
+      <c r="E600" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="F600" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="G600" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="H600" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="I600" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J600" t="b">
+        <v>0</v>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 307.92 &lt;= EMA21 309.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>182.91</v>
+      </c>
+      <c r="E601" t="n">
+        <v>210.39</v>
+      </c>
+      <c r="F601" t="n">
+        <v>210.39</v>
+      </c>
+      <c r="G601" t="n">
+        <v>181.58</v>
+      </c>
+      <c r="H601" t="n">
+        <v>185.82</v>
+      </c>
+      <c r="I601" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J601" t="b">
+        <v>0</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 181.58 &lt;= EMA21 185.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>1729.52</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1874.99</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1874.99</v>
+      </c>
+      <c r="G602" t="n">
+        <v>1717.98</v>
+      </c>
+      <c r="H602" t="n">
+        <v>1728.15</v>
+      </c>
+      <c r="I602" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J602" t="b">
+        <v>0</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1717.98 &lt;= EMA21 1728.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="E603" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="F603" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="G603" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="H603" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J603" t="b">
+        <v>0</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 363.13 &lt;= EMA21 367.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>235.01</v>
+      </c>
+      <c r="E604" t="n">
+        <v>252.79</v>
+      </c>
+      <c r="F604" t="n">
+        <v>252.79</v>
+      </c>
+      <c r="G604" t="n">
+        <v>223.49</v>
+      </c>
+      <c r="H604" t="n">
+        <v>222.55</v>
+      </c>
+      <c r="I604" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J604" t="b">
+        <v>0</v>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 235.01 &lt;= Upper 252.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>223.32</v>
+      </c>
+      <c r="E605" t="n">
+        <v>234.32</v>
+      </c>
+      <c r="F605" t="n">
+        <v>234.32</v>
+      </c>
+      <c r="G605" t="n">
+        <v>225.13</v>
+      </c>
+      <c r="H605" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="I605" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J605" t="b">
+        <v>0</v>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 225.13 &lt;= EMA21 229.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="E606" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="F606" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="G606" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="H606" t="n">
+        <v>75.62</v>
+      </c>
+      <c r="I606" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J606" t="b">
+        <v>0</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 72.90 &lt;= EMA21 75.62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>1203.75</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1431.71</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1431.71</v>
+      </c>
+      <c r="G607" t="n">
+        <v>1237.52</v>
+      </c>
+      <c r="H607" t="n">
+        <v>1278.16</v>
+      </c>
+      <c r="I607" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J607" t="b">
+        <v>0</v>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1237.52 &lt;= EMA21 1278.16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="E608" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="F608" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="G608" t="n">
+        <v>72</v>
+      </c>
+      <c r="H608" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J608" t="b">
+        <v>0</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.83x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>105.24</v>
+      </c>
+      <c r="E609" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="F609" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="G609" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="H609" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="I609" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J609" t="b">
+        <v>0</v>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.04x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>383.69</v>
+      </c>
+      <c r="E610" t="n">
+        <v>432.48</v>
+      </c>
+      <c r="F610" t="n">
+        <v>432.48</v>
+      </c>
+      <c r="G610" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="H610" t="n">
+        <v>367.12</v>
+      </c>
+      <c r="I610" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J610" t="b">
+        <v>0</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 363.02 &lt;= EMA21 367.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>143.03</v>
+      </c>
+      <c r="E611" t="n">
+        <v>165.68</v>
+      </c>
+      <c r="F611" t="n">
+        <v>165.68</v>
+      </c>
+      <c r="G611" t="n">
+        <v>138.59</v>
+      </c>
+      <c r="H611" t="n">
+        <v>140.13</v>
+      </c>
+      <c r="I611" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J611" t="b">
+        <v>0</v>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 138.59 &lt;= EMA21 140.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="E612" t="n">
+        <v>79.81999999999999</v>
+      </c>
+      <c r="F612" t="n">
+        <v>79.81999999999999</v>
+      </c>
+      <c r="G612" t="n">
+        <v>73.56</v>
+      </c>
+      <c r="H612" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J612" t="b">
+        <v>0</v>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.56 &lt;= EMA21 75.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="E613" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F613" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G613" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="H613" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="I613" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J613" t="b">
+        <v>0</v>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 38.93 &lt;= Upper 40.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>535.25</v>
+      </c>
+      <c r="E614" t="n">
+        <v>542.76</v>
+      </c>
+      <c r="F614" t="n">
+        <v>542.76</v>
+      </c>
+      <c r="G614" t="n">
+        <v>500.27</v>
+      </c>
+      <c r="H614" t="n">
+        <v>476.53</v>
+      </c>
+      <c r="I614" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J614" t="b">
+        <v>0</v>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 535.25 &lt;= Upper 542.76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="E615" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="F615" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="G615" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="H615" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="I615" t="n">
+        <v>1</v>
+      </c>
+      <c r="J615" t="b">
+        <v>0</v>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 32.39 &lt;= Upper 32.76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>482.28</v>
+      </c>
+      <c r="E616" t="n">
+        <v>516.8</v>
+      </c>
+      <c r="F616" t="n">
+        <v>516.8</v>
+      </c>
+      <c r="G616" t="n">
+        <v>465.08</v>
+      </c>
+      <c r="H616" t="n">
+        <v>470.42</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J616" t="b">
+        <v>0</v>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 465.08 &lt;= EMA21 470.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>885.92</v>
+      </c>
+      <c r="E617" t="n">
+        <v>971.3099999999999</v>
+      </c>
+      <c r="F617" t="n">
+        <v>971.3099999999999</v>
+      </c>
+      <c r="G617" t="n">
+        <v>852.87</v>
+      </c>
+      <c r="H617" t="n">
+        <v>850.46</v>
+      </c>
+      <c r="I617" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J617" t="b">
+        <v>0</v>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 885.92 &lt;= Upper 971.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>192.93</v>
+      </c>
+      <c r="E618" t="n">
+        <v>208.18</v>
+      </c>
+      <c r="F618" t="n">
+        <v>208.18</v>
+      </c>
+      <c r="G618" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="H618" t="n">
+        <v>191.69</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J618" t="b">
+        <v>0</v>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 192.93 &lt;= Upper 208.18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>109.43</v>
+      </c>
+      <c r="E619" t="n">
+        <v>117.82</v>
+      </c>
+      <c r="F619" t="n">
+        <v>117.82</v>
+      </c>
+      <c r="G619" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="H619" t="n">
+        <v>111.47</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J619" t="b">
+        <v>0</v>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 109.85 &lt;= EMA21 111.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="E620" t="n">
+        <v>195.29</v>
+      </c>
+      <c r="F620" t="n">
+        <v>195.29</v>
+      </c>
+      <c r="G620" t="n">
+        <v>183.72</v>
+      </c>
+      <c r="H620" t="n">
+        <v>180.77</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J620" t="b">
+        <v>0</v>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 175.80 &lt;= Upper 195.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>239.94</v>
+      </c>
+      <c r="E621" t="n">
+        <v>239.95</v>
+      </c>
+      <c r="F621" t="n">
+        <v>239.95</v>
+      </c>
+      <c r="G621" t="n">
+        <v>234.78</v>
+      </c>
+      <c r="H621" t="n">
+        <v>234.24</v>
+      </c>
+      <c r="I621" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J621" t="b">
+        <v>0</v>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 239.94 &lt;= Upper 239.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>131.11</v>
+      </c>
+      <c r="E622" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="F622" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="G622" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="H622" t="n">
+        <v>131.86</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J622" t="b">
+        <v>0</v>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 131.11 &lt;= Upper 149.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="E623" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="F623" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="G623" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="H623" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="I623" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J623" t="b">
+        <v>0</v>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 335.33 &lt;= EMA21 338.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="E624" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="F624" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="G624" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="H624" t="n">
+        <v>350.74</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J624" t="b">
+        <v>0</v>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 344.25 &lt;= EMA21 350.74)</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>207.8</v>
+      </c>
+      <c r="E625" t="n">
+        <v>236.53</v>
+      </c>
+      <c r="F625" t="n">
+        <v>236.53</v>
+      </c>
+      <c r="G625" t="n">
+        <v>210.52</v>
+      </c>
+      <c r="H625" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J625" t="b">
+        <v>0</v>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 207.80 &lt;= Upper 236.53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>331.48</v>
+      </c>
+      <c r="E626" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="F626" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="G626" t="n">
+        <v>331.07</v>
+      </c>
+      <c r="H626" t="n">
+        <v>324.33</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J626" t="b">
+        <v>0</v>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 331.48 &lt;= Upper 348.86)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>169.53</v>
+      </c>
+      <c r="E627" t="n">
+        <v>187.54</v>
+      </c>
+      <c r="F627" t="n">
+        <v>187.54</v>
+      </c>
+      <c r="G627" t="n">
+        <v>175</v>
+      </c>
+      <c r="H627" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J627" t="b">
+        <v>0</v>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 169.53 &lt;= Upper 187.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>225.27</v>
+      </c>
+      <c r="E628" t="n">
+        <v>259.03</v>
+      </c>
+      <c r="F628" t="n">
+        <v>259.03</v>
+      </c>
+      <c r="G628" t="n">
+        <v>221.72</v>
+      </c>
+      <c r="H628" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="I628" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J628" t="b">
+        <v>0</v>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 221.72 &lt;= EMA21 230.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="E629" t="n">
+        <v>193.9</v>
+      </c>
+      <c r="F629" t="n">
+        <v>193.9</v>
+      </c>
+      <c r="G629" t="n">
+        <v>172.33</v>
+      </c>
+      <c r="H629" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="I629" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J629" t="b">
+        <v>0</v>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 172.33 &lt;= EMA21 172.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>314.18</v>
+      </c>
+      <c r="E630" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="F630" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="G630" t="n">
+        <v>291.97</v>
+      </c>
+      <c r="H630" t="n">
+        <v>290.9</v>
+      </c>
+      <c r="I630" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J630" t="b">
+        <v>0</v>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 314.18 &lt;= Upper 327.11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>358.38</v>
+      </c>
+      <c r="E631" t="n">
+        <v>487.43</v>
+      </c>
+      <c r="F631" t="n">
+        <v>487.43</v>
+      </c>
+      <c r="G631" t="n">
+        <v>387.64</v>
+      </c>
+      <c r="H631" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="I631" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J631" t="b">
+        <v>0</v>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 387.64 &lt;= EMA21 397.39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>157.22</v>
+      </c>
+      <c r="E632" t="n">
+        <v>170.83</v>
+      </c>
+      <c r="F632" t="n">
+        <v>170.83</v>
+      </c>
+      <c r="G632" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="H632" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J632" t="b">
+        <v>0</v>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 158.52 &lt;= EMA21 158.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>177.74</v>
+      </c>
+      <c r="E633" t="n">
+        <v>199.94</v>
+      </c>
+      <c r="F633" t="n">
+        <v>199.94</v>
+      </c>
+      <c r="G633" t="n">
+        <v>182.05</v>
+      </c>
+      <c r="H633" t="n">
+        <v>169.85</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J633" t="b">
+        <v>0</v>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 177.74 &lt;= Upper 199.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>186.05</v>
+      </c>
+      <c r="E634" t="n">
+        <v>210.72</v>
+      </c>
+      <c r="F634" t="n">
+        <v>210.72</v>
+      </c>
+      <c r="G634" t="n">
+        <v>194.08</v>
+      </c>
+      <c r="H634" t="n">
+        <v>190.22</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J634" t="b">
+        <v>0</v>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 186.05 &lt;= Upper 210.72)</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>230.19</v>
+      </c>
+      <c r="E635" t="n">
+        <v>267.96</v>
+      </c>
+      <c r="F635" t="n">
+        <v>267.96</v>
+      </c>
+      <c r="G635" t="n">
+        <v>243.7</v>
+      </c>
+      <c r="H635" t="n">
+        <v>240.09</v>
+      </c>
+      <c r="I635" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J635" t="b">
+        <v>0</v>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 230.19 &lt;= Upper 267.96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="E636" t="n">
+        <v>293.48</v>
+      </c>
+      <c r="F636" t="n">
+        <v>293.48</v>
+      </c>
+      <c r="G636" t="n">
+        <v>269.02</v>
+      </c>
+      <c r="H636" t="n">
+        <v>257.11</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J636" t="b">
+        <v>0</v>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 260.80 &lt;= Upper 293.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>96.18000000000001</v>
+      </c>
+      <c r="E637" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="F637" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="G637" t="n">
+        <v>98.06999999999999</v>
+      </c>
+      <c r="H637" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J637" t="b">
+        <v>0</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 98.07 &lt;= EMA21 99.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>172.74</v>
+      </c>
+      <c r="E638" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="F638" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="G638" t="n">
+        <v>165.16</v>
+      </c>
+      <c r="H638" t="n">
+        <v>156.85</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J638" t="b">
+        <v>0</v>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 172.74 &lt;= Upper 185.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>305.06</v>
+      </c>
+      <c r="E639" t="n">
+        <v>321.51</v>
+      </c>
+      <c r="F639" t="n">
+        <v>321.51</v>
+      </c>
+      <c r="G639" t="n">
+        <v>312.78</v>
+      </c>
+      <c r="H639" t="n">
+        <v>324.94</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J639" t="b">
+        <v>0</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 312.78 &lt;= EMA21 324.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>490</v>
+      </c>
+      <c r="E640" t="n">
+        <v>678.04</v>
+      </c>
+      <c r="F640" t="n">
+        <v>678.04</v>
+      </c>
+      <c r="G640" t="n">
+        <v>532.85</v>
+      </c>
+      <c r="H640" t="n">
+        <v>557.49</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J640" t="b">
+        <v>0</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 532.85 &lt;= EMA21 557.49)</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="E641" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="F641" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="G641" t="n">
+        <v>304.02</v>
+      </c>
+      <c r="H641" t="n">
+        <v>316.71</v>
+      </c>
+      <c r="I641" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J641" t="b">
+        <v>0</v>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 304.02 &lt;= EMA21 316.71)</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>393.22</v>
+      </c>
+      <c r="E642" t="n">
+        <v>449.62</v>
+      </c>
+      <c r="F642" t="n">
+        <v>449.62</v>
+      </c>
+      <c r="G642" t="n">
+        <v>407.21</v>
+      </c>
+      <c r="H642" t="n">
+        <v>410.24</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J642" t="b">
+        <v>0</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 407.21 &lt;= EMA21 410.24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>206.62</v>
+      </c>
+      <c r="E643" t="n">
+        <v>278.47</v>
+      </c>
+      <c r="F643" t="n">
+        <v>278.47</v>
+      </c>
+      <c r="G643" t="n">
+        <v>230.84</v>
+      </c>
+      <c r="H643" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="I643" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J643" t="b">
+        <v>0</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 230.84 &lt;= EMA21 238.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ANSS</t>
+        </is>
+      </c>
+      <c r="J644" t="b">
+        <v>0</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>128.89</v>
+      </c>
+      <c r="E645" t="n">
+        <v>164.54</v>
+      </c>
+      <c r="F645" t="n">
+        <v>164.54</v>
+      </c>
+      <c r="G645" t="n">
+        <v>143.12</v>
+      </c>
+      <c r="H645" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="I645" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J645" t="b">
+        <v>0</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 143.12 &lt;= EMA21 145.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>TYL</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="E646" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="F646" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="G646" t="n">
+        <v>358.92</v>
+      </c>
+      <c r="H646" t="n">
+        <v>350.86</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J646" t="b">
+        <v>0</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 342.68 &lt;= Upper 390.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="E647" t="n">
+        <v>161.39</v>
+      </c>
+      <c r="F647" t="n">
+        <v>161.39</v>
+      </c>
+      <c r="G647" t="n">
+        <v>150.12</v>
+      </c>
+      <c r="H647" t="n">
+        <v>149.19</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J647" t="b">
+        <v>0</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 142.10 &lt;= Upper 161.39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>169.69</v>
+      </c>
+      <c r="E648" t="n">
+        <v>206.94</v>
+      </c>
+      <c r="F648" t="n">
+        <v>206.94</v>
+      </c>
+      <c r="G648" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="H648" t="n">
+        <v>183.98</v>
+      </c>
+      <c r="I648" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J648" t="b">
+        <v>0</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 169.69 &lt;= Upper 206.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E649" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="F649" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="G649" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="H649" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="I649" t="n">
+        <v>1</v>
+      </c>
+      <c r="J649" t="b">
+        <v>0</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 58.20 &lt;= Upper 66.36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="E650" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F650" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="G650" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="H650" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="I650" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J650" t="b">
+        <v>0</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 11.61 &lt;= EMA21 11.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>114.68</v>
+      </c>
+      <c r="E651" t="n">
+        <v>123.83</v>
+      </c>
+      <c r="F651" t="n">
+        <v>123.83</v>
+      </c>
+      <c r="G651" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="H651" t="n">
+        <v>110.78</v>
+      </c>
+      <c r="I651" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J651" t="b">
+        <v>0</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 114.68 &lt;= Upper 123.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="E652" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="F652" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="G652" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="H652" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I652" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J652" t="b">
+        <v>0</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 29.76 &lt;= Upper 31.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>142.37</v>
+      </c>
+      <c r="E653" t="n">
+        <v>156.44</v>
+      </c>
+      <c r="F653" t="n">
+        <v>156.44</v>
+      </c>
+      <c r="G653" t="n">
+        <v>146.51</v>
+      </c>
+      <c r="H653" t="n">
+        <v>143.91</v>
+      </c>
+      <c r="I653" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J653" t="b">
+        <v>0</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 142.37 &lt;= Upper 156.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="E654" t="n">
+        <v>419.98</v>
+      </c>
+      <c r="F654" t="n">
+        <v>419.98</v>
+      </c>
+      <c r="G654" t="n">
+        <v>395.51</v>
+      </c>
+      <c r="H654" t="n">
+        <v>396.66</v>
+      </c>
+      <c r="I654" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J654" t="b">
+        <v>0</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 395.51 &lt;= EMA21 396.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="J655" t="b">
+        <v>0</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="E656" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="F656" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="G656" t="n">
+        <v>107.87</v>
+      </c>
+      <c r="H656" t="n">
+        <v>110.47</v>
+      </c>
+      <c r="I656" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J656" t="b">
+        <v>0</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 107.87 &lt;= EMA21 110.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="J657" t="b">
+        <v>0</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>211.14</v>
+      </c>
+      <c r="E658" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="F658" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="G658" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="H658" t="n">
+        <v>227.02</v>
+      </c>
+      <c r="I658" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J658" t="b">
+        <v>0</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 218.75 &lt;= EMA21 227.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="E659" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="F659" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="G659" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="H659" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J659" t="b">
+        <v>0</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 44.52 &lt;= Upper 44.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="E660" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="F660" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="G660" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="H660" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="I660" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J660" t="b">
+        <v>0</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 42.54 &lt;= Upper 48.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="E661" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="F661" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="G661" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="H661" t="n">
+        <v>78.65000000000001</v>
+      </c>
+      <c r="I661" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J661" t="b">
+        <v>0</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 76.03 &lt;= Upper 84.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="E662" t="n">
+        <v>111.19</v>
+      </c>
+      <c r="F662" t="n">
+        <v>111.19</v>
+      </c>
+      <c r="G662" t="n">
+        <v>106.14</v>
+      </c>
+      <c r="H662" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="I662" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J662" t="b">
+        <v>0</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 104.18 &lt;= Upper 111.19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="E663" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="F663" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="G663" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="H663" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="I663" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J663" t="b">
+        <v>0</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 27.91 &lt;= Upper 29.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>PARA</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E664" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F664" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G664" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H664" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I664" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J664" t="b">
+        <v>0</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1.10 &lt;= EMA21 1.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>523</v>
+      </c>
+      <c r="E665" t="n">
+        <v>572.8</v>
+      </c>
+      <c r="F665" t="n">
+        <v>572.8</v>
+      </c>
+      <c r="G665" t="n">
+        <v>537.99</v>
+      </c>
+      <c r="H665" t="n">
+        <v>530.0700000000001</v>
+      </c>
+      <c r="I665" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J665" t="b">
+        <v>0</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 523.00 &lt;= Upper 572.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>TME</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="E666" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="F666" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="G666" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H666" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="I666" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J666" t="b">
+        <v>0</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 8.26 &lt;= EMA21 8.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>105.83</v>
+      </c>
+      <c r="E667" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="F667" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="G667" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="H667" t="n">
+        <v>107.63</v>
+      </c>
+      <c r="I667" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J667" t="b">
+        <v>0</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 106.32 &lt;= EMA21 107.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>902.6</v>
+      </c>
+      <c r="E668" t="n">
+        <v>980.83</v>
+      </c>
+      <c r="F668" t="n">
+        <v>980.83</v>
+      </c>
+      <c r="G668" t="n">
+        <v>924.5700000000001</v>
+      </c>
+      <c r="H668" t="n">
+        <v>936.24</v>
+      </c>
+      <c r="I668" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J668" t="b">
+        <v>0</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 924.57 &lt;= EMA21 936.24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>157.52</v>
+      </c>
+      <c r="E669" t="n">
+        <v>170.88</v>
+      </c>
+      <c r="F669" t="n">
+        <v>170.88</v>
+      </c>
+      <c r="G669" t="n">
+        <v>161.91</v>
+      </c>
+      <c r="H669" t="n">
+        <v>159</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J669" t="b">
+        <v>0</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 157.52 &lt;= Upper 170.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>310.45</v>
+      </c>
+      <c r="E670" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="F670" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="G670" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="H670" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J670" t="b">
+        <v>0</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 319.47 &lt;= EMA21 326.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="E671" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="F671" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="G671" t="n">
+        <v>203.48</v>
+      </c>
+      <c r="H671" t="n">
+        <v>207.91</v>
+      </c>
+      <c r="I671" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J671" t="b">
+        <v>0</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 203.48 &lt;= EMA21 207.91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="E672" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="F672" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="G672" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H672" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="I672" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J672" t="b">
+        <v>0</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 56.44 &lt;= Upper 59.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E673" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="F673" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="G673" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="H673" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="I673" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J673" t="b">
+        <v>0</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 12.28 &lt;= EMA21 12.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>124.57</v>
+      </c>
+      <c r="E674" t="n">
+        <v>133.03</v>
+      </c>
+      <c r="F674" t="n">
+        <v>133.03</v>
+      </c>
+      <c r="G674" t="n">
+        <v>127.68</v>
+      </c>
+      <c r="H674" t="n">
+        <v>126</v>
+      </c>
+      <c r="I674" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J674" t="b">
+        <v>0</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 124.57 &lt;= Upper 133.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>118.39</v>
+      </c>
+      <c r="E675" t="n">
+        <v>137.37</v>
+      </c>
+      <c r="F675" t="n">
+        <v>137.37</v>
+      </c>
+      <c r="G675" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="H675" t="n">
+        <v>128.42</v>
+      </c>
+      <c r="I675" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J675" t="b">
+        <v>0</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 127.20 &lt;= EMA21 128.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>BJ</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="E676" t="n">
+        <v>97.22</v>
+      </c>
+      <c r="F676" t="n">
+        <v>97.22</v>
+      </c>
+      <c r="G676" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="H676" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="I676" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J676" t="b">
+        <v>0</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 91.41 &lt;= EMA21 92.46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>225.27</v>
+      </c>
+      <c r="E677" t="n">
+        <v>247.52</v>
+      </c>
+      <c r="F677" t="n">
+        <v>247.52</v>
+      </c>
+      <c r="G677" t="n">
+        <v>230.05</v>
+      </c>
+      <c r="H677" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="I677" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J677" t="b">
+        <v>0</v>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 230.05 &lt;= EMA21 233.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>126.12</v>
+      </c>
+      <c r="E678" t="n">
+        <v>156.65</v>
+      </c>
+      <c r="F678" t="n">
+        <v>156.65</v>
+      </c>
+      <c r="G678" t="n">
+        <v>132.22</v>
+      </c>
+      <c r="H678" t="n">
+        <v>138.63</v>
+      </c>
+      <c r="I678" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J678" t="b">
+        <v>0</v>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 132.22 &lt;= EMA21 138.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="E679" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F679" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="G679" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="H679" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="I679" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J679" t="b">
+        <v>0</v>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 38.35 &lt;= EMA21 39.19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="E680" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="F680" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="G680" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="H680" t="n">
+        <v>115.04</v>
+      </c>
+      <c r="I680" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J680" t="b">
+        <v>0</v>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 110.60 &lt;= EMA21 115.04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="E681" t="n">
+        <v>110.39</v>
+      </c>
+      <c r="F681" t="n">
+        <v>110.39</v>
+      </c>
+      <c r="G681" t="n">
+        <v>104.24</v>
+      </c>
+      <c r="H681" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="I681" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J681" t="b">
+        <v>0</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 104.24 &lt;= EMA21 105.15)</t>
         </is>
       </c>
     </row>
@@ -25172,7 +29418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25486,6 +29732,68 @@
         <v>1.52</v>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>653.6900000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>624.27</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>168.46</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -25565,34 +29873,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>524.14</v>
+        <v>174.09</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>1572.42</v>
+        <v>1914.99</v>
       </c>
       <c r="F2" t="n">
-        <v>524.14</v>
+        <v>174.09</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>500.55</v>
+        <v>166.26</v>
       </c>
       <c r="I2" t="n">
-        <v>524.14</v>
+        <v>174.09</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -25606,7 +29914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -25615,25 +29923,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>174.09</v>
+        <v>162.52</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>1914.99</v>
+        <v>1950.24</v>
       </c>
       <c r="F3" t="n">
-        <v>174.09</v>
+        <v>162.52</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>166.26</v>
+        <v>155.21</v>
       </c>
       <c r="I3" t="n">
-        <v>174.09</v>
+        <v>162.52</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -25647,7 +29955,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -25656,25 +29964,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>162.52</v>
+        <v>104.07</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>1950.24</v>
+        <v>1977.33</v>
       </c>
       <c r="F4" t="n">
-        <v>162.52</v>
+        <v>104.07</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>155.21</v>
+        <v>99.39</v>
       </c>
       <c r="I4" t="n">
-        <v>162.52</v>
+        <v>104.07</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -25688,34 +29996,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>104.07</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1977.33</v>
+        <v>1961.07</v>
       </c>
       <c r="F5" t="n">
-        <v>104.07</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>99.39</v>
+        <v>624.27</v>
       </c>
       <c r="I5" t="n">
-        <v>104.07</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -25737,7 +30045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25904,6 +30212,57 @@
         <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>524.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>537.66</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1572.42</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>TRAILING_STOP</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -25920,7 +30279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26318,6 +30677,104 @@
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:43:35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27F84F6838</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>537.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>537.66</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>TRAILING_STOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:43:35</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>193A12ACFF</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>653.6900000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>653.6900000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Entry Breakout</t>
         </is>
@@ -26402,7 +30859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26782,6 +31239,39 @@
         <v>4</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>04:43:36</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2064.86</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7803.63</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9868.49</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-131.51</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K681"/>
+  <dimension ref="A1:K781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29404,6 +29404,4252 @@
       <c r="K681" t="inlineStr">
         <is>
           <t>EMA_BEARISH (EMA9 104.24 &lt;= EMA21 105.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>326.57</v>
+      </c>
+      <c r="E682" t="n">
+        <v>329.42</v>
+      </c>
+      <c r="F682" t="n">
+        <v>329.42</v>
+      </c>
+      <c r="G682" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="H682" t="n">
+        <v>317.47</v>
+      </c>
+      <c r="I682" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J682" t="b">
+        <v>0</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 326.57 &lt;= Upper 329.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>492.44</v>
+      </c>
+      <c r="E683" t="n">
+        <v>514.15</v>
+      </c>
+      <c r="F683" t="n">
+        <v>514.15</v>
+      </c>
+      <c r="G683" t="n">
+        <v>496.63</v>
+      </c>
+      <c r="H683" t="n">
+        <v>489.67</v>
+      </c>
+      <c r="I683" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J683" t="b">
+        <v>0</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 492.44 &lt;= Upper 514.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>218.36</v>
+      </c>
+      <c r="E684" t="n">
+        <v>232.91</v>
+      </c>
+      <c r="F684" t="n">
+        <v>232.91</v>
+      </c>
+      <c r="G684" t="n">
+        <v>222.47</v>
+      </c>
+      <c r="H684" t="n">
+        <v>219.86</v>
+      </c>
+      <c r="I684" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J684" t="b">
+        <v>0</v>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 218.36 &lt;= Upper 232.91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="E685" t="n">
+        <v>351</v>
+      </c>
+      <c r="F685" t="n">
+        <v>351</v>
+      </c>
+      <c r="G685" t="n">
+        <v>337.11</v>
+      </c>
+      <c r="H685" t="n">
+        <v>340.97</v>
+      </c>
+      <c r="I685" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J685" t="b">
+        <v>0</v>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 337.11 &lt;= EMA21 340.97)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>330.39</v>
+      </c>
+      <c r="E686" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="F686" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="G686" t="n">
+        <v>334.27</v>
+      </c>
+      <c r="H686" t="n">
+        <v>338.27</v>
+      </c>
+      <c r="I686" t="n">
+        <v>1</v>
+      </c>
+      <c r="J686" t="b">
+        <v>0</v>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 334.27 &lt;= EMA21 338.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>251.89</v>
+      </c>
+      <c r="E687" t="n">
+        <v>267.48</v>
+      </c>
+      <c r="F687" t="n">
+        <v>267.48</v>
+      </c>
+      <c r="G687" t="n">
+        <v>256.24</v>
+      </c>
+      <c r="H687" t="n">
+        <v>258.06</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J687" t="b">
+        <v>0</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 256.24 &lt;= EMA21 258.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>644.38</v>
+      </c>
+      <c r="E688" t="n">
+        <v>646.3099999999999</v>
+      </c>
+      <c r="F688" t="n">
+        <v>646.3099999999999</v>
+      </c>
+      <c r="G688" t="n">
+        <v>613.89</v>
+      </c>
+      <c r="H688" t="n">
+        <v>597.17</v>
+      </c>
+      <c r="I688" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J688" t="b">
+        <v>0</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 644.38 &lt;= Upper 646.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="E689" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="F689" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="G689" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="H689" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J689" t="b">
+        <v>0</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 363.56 &lt;= Upper 376.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="E690" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="F690" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="G690" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="H690" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J690" t="b">
+        <v>0</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 364.66 &lt;= EMA21 371.69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>152.94</v>
+      </c>
+      <c r="E691" t="n">
+        <v>162.59</v>
+      </c>
+      <c r="F691" t="n">
+        <v>162.59</v>
+      </c>
+      <c r="G691" t="n">
+        <v>154.12</v>
+      </c>
+      <c r="H691" t="n">
+        <v>150</v>
+      </c>
+      <c r="I691" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J691" t="b">
+        <v>0</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 152.94 &lt;= Upper 162.59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>243</v>
+      </c>
+      <c r="E692" t="n">
+        <v>282.64</v>
+      </c>
+      <c r="F692" t="n">
+        <v>282.64</v>
+      </c>
+      <c r="G692" t="n">
+        <v>246.12</v>
+      </c>
+      <c r="H692" t="n">
+        <v>230.91</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J692" t="b">
+        <v>0</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 243.00 &lt;= Upper 282.64)</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>248.83</v>
+      </c>
+      <c r="E693" t="n">
+        <v>298.07</v>
+      </c>
+      <c r="F693" t="n">
+        <v>298.07</v>
+      </c>
+      <c r="G693" t="n">
+        <v>266.39</v>
+      </c>
+      <c r="H693" t="n">
+        <v>267.65</v>
+      </c>
+      <c r="I693" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J693" t="b">
+        <v>0</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 266.39 &lt;= EMA21 267.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>503.6</v>
+      </c>
+      <c r="E694" t="n">
+        <v>520.11</v>
+      </c>
+      <c r="F694" t="n">
+        <v>520.11</v>
+      </c>
+      <c r="G694" t="n">
+        <v>488.59</v>
+      </c>
+      <c r="H694" t="n">
+        <v>484.1</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J694" t="b">
+        <v>0</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 503.60 &lt;= Upper 520.11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="E695" t="n">
+        <v>107.72</v>
+      </c>
+      <c r="F695" t="n">
+        <v>107.72</v>
+      </c>
+      <c r="G695" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="H695" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="I695" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J695" t="b">
+        <v>0</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 100.32 &lt;= Upper 107.72)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>977.41</v>
+      </c>
+      <c r="E696" t="n">
+        <v>1025.54</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1025.54</v>
+      </c>
+      <c r="G696" t="n">
+        <v>979.48</v>
+      </c>
+      <c r="H696" t="n">
+        <v>957.85</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J696" t="b">
+        <v>0</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 977.41 &lt;= Upper 1025.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="E697" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="F697" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="G697" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="H697" t="n">
+        <v>167.65</v>
+      </c>
+      <c r="I697" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J697" t="b">
+        <v>1</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>258.82</v>
+      </c>
+      <c r="E698" t="n">
+        <v>279.83</v>
+      </c>
+      <c r="F698" t="n">
+        <v>279.83</v>
+      </c>
+      <c r="G698" t="n">
+        <v>259.37</v>
+      </c>
+      <c r="H698" t="n">
+        <v>264.03</v>
+      </c>
+      <c r="I698" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J698" t="b">
+        <v>0</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 259.37 &lt;= EMA21 264.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>454.01</v>
+      </c>
+      <c r="E699" t="n">
+        <v>537.08</v>
+      </c>
+      <c r="F699" t="n">
+        <v>537.08</v>
+      </c>
+      <c r="G699" t="n">
+        <v>461.41</v>
+      </c>
+      <c r="H699" t="n">
+        <v>477.89</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J699" t="b">
+        <v>0</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 461.41 &lt;= EMA21 477.89)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="E700" t="n">
+        <v>342.41</v>
+      </c>
+      <c r="F700" t="n">
+        <v>342.41</v>
+      </c>
+      <c r="G700" t="n">
+        <v>305.94</v>
+      </c>
+      <c r="H700" t="n">
+        <v>308.75</v>
+      </c>
+      <c r="I700" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J700" t="b">
+        <v>0</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 305.94 &lt;= EMA21 308.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>177.18</v>
+      </c>
+      <c r="E701" t="n">
+        <v>206.96</v>
+      </c>
+      <c r="F701" t="n">
+        <v>206.96</v>
+      </c>
+      <c r="G701" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="H701" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="I701" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J701" t="b">
+        <v>0</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 180.70 &lt;= EMA21 185.04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>1687.43</v>
+      </c>
+      <c r="E702" t="n">
+        <v>1868.62</v>
+      </c>
+      <c r="F702" t="n">
+        <v>1868.62</v>
+      </c>
+      <c r="G702" t="n">
+        <v>1711.87</v>
+      </c>
+      <c r="H702" t="n">
+        <v>1724.44</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J702" t="b">
+        <v>0</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1711.87 &lt;= EMA21 1724.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>361.25</v>
+      </c>
+      <c r="E703" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="F703" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="G703" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="H703" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="I703" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J703" t="b">
+        <v>0</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 362.75 &lt;= EMA21 367.07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>226.96</v>
+      </c>
+      <c r="E704" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="F704" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="G704" t="n">
+        <v>224.18</v>
+      </c>
+      <c r="H704" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="I704" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J704" t="b">
+        <v>0</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 226.96 &lt;= Upper 252.90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>226.46</v>
+      </c>
+      <c r="E705" t="n">
+        <v>233.27</v>
+      </c>
+      <c r="F705" t="n">
+        <v>233.27</v>
+      </c>
+      <c r="G705" t="n">
+        <v>225.39</v>
+      </c>
+      <c r="H705" t="n">
+        <v>229.08</v>
+      </c>
+      <c r="I705" t="n">
+        <v>1</v>
+      </c>
+      <c r="J705" t="b">
+        <v>0</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 225.39 &lt;= EMA21 229.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="E706" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="F706" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="G706" t="n">
+        <v>72.34999999999999</v>
+      </c>
+      <c r="H706" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="I706" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J706" t="b">
+        <v>0</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 72.35 &lt;= EMA21 75.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>1186.08</v>
+      </c>
+      <c r="E707" t="n">
+        <v>1413.53</v>
+      </c>
+      <c r="F707" t="n">
+        <v>1413.53</v>
+      </c>
+      <c r="G707" t="n">
+        <v>1227.23</v>
+      </c>
+      <c r="H707" t="n">
+        <v>1269.79</v>
+      </c>
+      <c r="I707" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J707" t="b">
+        <v>0</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1227.23 &lt;= EMA21 1269.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="E708" t="n">
+        <v>79.03</v>
+      </c>
+      <c r="F708" t="n">
+        <v>79.03</v>
+      </c>
+      <c r="G708" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="H708" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="I708" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J708" t="b">
+        <v>1</v>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="E709" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="F709" t="n">
+        <v>107.64</v>
+      </c>
+      <c r="G709" t="n">
+        <v>103.09</v>
+      </c>
+      <c r="H709" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="I709" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J709" t="b">
+        <v>1</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="E710" t="n">
+        <v>429.47</v>
+      </c>
+      <c r="F710" t="n">
+        <v>429.47</v>
+      </c>
+      <c r="G710" t="n">
+        <v>364.46</v>
+      </c>
+      <c r="H710" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="I710" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J710" t="b">
+        <v>0</v>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 364.46 &lt;= EMA21 367.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="E711" t="n">
+        <v>163.12</v>
+      </c>
+      <c r="F711" t="n">
+        <v>163.12</v>
+      </c>
+      <c r="G711" t="n">
+        <v>138.36</v>
+      </c>
+      <c r="H711" t="n">
+        <v>139.88</v>
+      </c>
+      <c r="I711" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J711" t="b">
+        <v>0</v>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 138.36 &lt;= EMA21 139.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="E712" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="F712" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="G712" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="H712" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J712" t="b">
+        <v>0</v>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.16 &lt;= EMA21 74.70)</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="E713" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="F713" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="G713" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="H713" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J713" t="b">
+        <v>0</v>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 37.38 &lt;= Upper 40.39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>506.62</v>
+      </c>
+      <c r="E714" t="n">
+        <v>545.25</v>
+      </c>
+      <c r="F714" t="n">
+        <v>545.25</v>
+      </c>
+      <c r="G714" t="n">
+        <v>501.54</v>
+      </c>
+      <c r="H714" t="n">
+        <v>479.26</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J714" t="b">
+        <v>0</v>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 506.62 &lt;= Upper 545.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="E715" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="F715" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="G715" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="H715" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="I715" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J715" t="b">
+        <v>0</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 32.73 &lt;= Upper 32.89)</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>460.93</v>
+      </c>
+      <c r="E716" t="n">
+        <v>516.8200000000001</v>
+      </c>
+      <c r="F716" t="n">
+        <v>516.8200000000001</v>
+      </c>
+      <c r="G716" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="H716" t="n">
+        <v>469.55</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J716" t="b">
+        <v>0</v>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 464.25 &lt;= EMA21 469.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>862.33</v>
+      </c>
+      <c r="E717" t="n">
+        <v>970.25</v>
+      </c>
+      <c r="F717" t="n">
+        <v>970.25</v>
+      </c>
+      <c r="G717" t="n">
+        <v>854.76</v>
+      </c>
+      <c r="H717" t="n">
+        <v>851.54</v>
+      </c>
+      <c r="I717" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J717" t="b">
+        <v>0</v>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 862.33 &lt;= Upper 970.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>188.99</v>
+      </c>
+      <c r="E718" t="n">
+        <v>205.02</v>
+      </c>
+      <c r="F718" t="n">
+        <v>205.02</v>
+      </c>
+      <c r="G718" t="n">
+        <v>192.16</v>
+      </c>
+      <c r="H718" t="n">
+        <v>191.44</v>
+      </c>
+      <c r="I718" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J718" t="b">
+        <v>0</v>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 188.99 &lt;= Upper 205.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="E719" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="F719" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="G719" t="n">
+        <v>109.36</v>
+      </c>
+      <c r="H719" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="I719" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J719" t="b">
+        <v>0</v>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 109.36 &lt;= EMA21 111.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>177.91</v>
+      </c>
+      <c r="E720" t="n">
+        <v>195.32</v>
+      </c>
+      <c r="F720" t="n">
+        <v>195.32</v>
+      </c>
+      <c r="G720" t="n">
+        <v>182.56</v>
+      </c>
+      <c r="H720" t="n">
+        <v>180.51</v>
+      </c>
+      <c r="I720" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J720" t="b">
+        <v>0</v>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 177.91 &lt;= Upper 195.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>234.02</v>
+      </c>
+      <c r="E721" t="n">
+        <v>239.79</v>
+      </c>
+      <c r="F721" t="n">
+        <v>239.79</v>
+      </c>
+      <c r="G721" t="n">
+        <v>234.63</v>
+      </c>
+      <c r="H721" t="n">
+        <v>234.22</v>
+      </c>
+      <c r="I721" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J721" t="b">
+        <v>0</v>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 234.02 &lt;= Upper 239.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>131.17</v>
+      </c>
+      <c r="E722" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="F722" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="G722" t="n">
+        <v>135.51</v>
+      </c>
+      <c r="H722" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="I722" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J722" t="b">
+        <v>0</v>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 131.17 &lt;= Upper 149.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>312.77</v>
+      </c>
+      <c r="E723" t="n">
+        <v>380</v>
+      </c>
+      <c r="F723" t="n">
+        <v>380</v>
+      </c>
+      <c r="G723" t="n">
+        <v>330.82</v>
+      </c>
+      <c r="H723" t="n">
+        <v>335.93</v>
+      </c>
+      <c r="I723" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J723" t="b">
+        <v>0</v>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 330.82 &lt;= EMA21 335.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>338.49</v>
+      </c>
+      <c r="E724" t="n">
+        <v>398.52</v>
+      </c>
+      <c r="F724" t="n">
+        <v>398.52</v>
+      </c>
+      <c r="G724" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="H724" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J724" t="b">
+        <v>0</v>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 343.10 &lt;= EMA21 349.62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>208.86</v>
+      </c>
+      <c r="E725" t="n">
+        <v>235.22</v>
+      </c>
+      <c r="F725" t="n">
+        <v>235.22</v>
+      </c>
+      <c r="G725" t="n">
+        <v>210.19</v>
+      </c>
+      <c r="H725" t="n">
+        <v>208.3</v>
+      </c>
+      <c r="I725" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J725" t="b">
+        <v>0</v>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 208.86 &lt;= Upper 235.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="E726" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="F726" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="G726" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="H726" t="n">
+        <v>324.82</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J726" t="b">
+        <v>0</v>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 329.72 &lt;= Upper 348.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>165.86</v>
+      </c>
+      <c r="E727" t="n">
+        <v>188.03</v>
+      </c>
+      <c r="F727" t="n">
+        <v>188.03</v>
+      </c>
+      <c r="G727" t="n">
+        <v>173.17</v>
+      </c>
+      <c r="H727" t="n">
+        <v>171.08</v>
+      </c>
+      <c r="I727" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J727" t="b">
+        <v>0</v>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 165.86 &lt;= Upper 188.03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>221.72</v>
+      </c>
+      <c r="E728" t="n">
+        <v>258.05</v>
+      </c>
+      <c r="F728" t="n">
+        <v>258.05</v>
+      </c>
+      <c r="G728" t="n">
+        <v>221.72</v>
+      </c>
+      <c r="H728" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="I728" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J728" t="b">
+        <v>0</v>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 221.72 &lt;= EMA21 229.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>163.48</v>
+      </c>
+      <c r="E729" t="n">
+        <v>194.51</v>
+      </c>
+      <c r="F729" t="n">
+        <v>194.51</v>
+      </c>
+      <c r="G729" t="n">
+        <v>170.56</v>
+      </c>
+      <c r="H729" t="n">
+        <v>171.91</v>
+      </c>
+      <c r="I729" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J729" t="b">
+        <v>0</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 170.56 &lt;= EMA21 171.91)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>311.17</v>
+      </c>
+      <c r="E730" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="F730" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="G730" t="n">
+        <v>295.81</v>
+      </c>
+      <c r="H730" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="I730" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J730" t="b">
+        <v>0</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 311.17 &lt;= Upper 327.07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="E731" t="n">
+        <v>486.32</v>
+      </c>
+      <c r="F731" t="n">
+        <v>486.32</v>
+      </c>
+      <c r="G731" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="H731" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="I731" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J731" t="b">
+        <v>0</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 384.88 &lt;= EMA21 395.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>158.85</v>
+      </c>
+      <c r="E732" t="n">
+        <v>170.69</v>
+      </c>
+      <c r="F732" t="n">
+        <v>170.69</v>
+      </c>
+      <c r="G732" t="n">
+        <v>158.59</v>
+      </c>
+      <c r="H732" t="n">
+        <v>158.81</v>
+      </c>
+      <c r="I732" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J732" t="b">
+        <v>0</v>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 158.59 &lt;= EMA21 158.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>179.57</v>
+      </c>
+      <c r="E733" t="n">
+        <v>199.19</v>
+      </c>
+      <c r="F733" t="n">
+        <v>199.19</v>
+      </c>
+      <c r="G733" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="H733" t="n">
+        <v>170.73</v>
+      </c>
+      <c r="I733" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J733" t="b">
+        <v>0</v>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 179.57 &lt;= Upper 199.19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>185.09</v>
+      </c>
+      <c r="E734" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="F734" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="G734" t="n">
+        <v>192.28</v>
+      </c>
+      <c r="H734" t="n">
+        <v>189.75</v>
+      </c>
+      <c r="I734" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J734" t="b">
+        <v>0</v>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 185.09 &lt;= Upper 208.90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>223.55</v>
+      </c>
+      <c r="E735" t="n">
+        <v>266.1</v>
+      </c>
+      <c r="F735" t="n">
+        <v>266.1</v>
+      </c>
+      <c r="G735" t="n">
+        <v>239.67</v>
+      </c>
+      <c r="H735" t="n">
+        <v>238.58</v>
+      </c>
+      <c r="I735" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J735" t="b">
+        <v>0</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 223.55 &lt;= Upper 266.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>260.98</v>
+      </c>
+      <c r="E736" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="F736" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="G736" t="n">
+        <v>267.41</v>
+      </c>
+      <c r="H736" t="n">
+        <v>257.47</v>
+      </c>
+      <c r="I736" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J736" t="b">
+        <v>0</v>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 260.98 &lt;= Upper 293.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="E737" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="F737" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="G737" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="H737" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="I737" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J737" t="b">
+        <v>0</v>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 97.55 &lt;= EMA21 98.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>171.11</v>
+      </c>
+      <c r="E738" t="n">
+        <v>187.32</v>
+      </c>
+      <c r="F738" t="n">
+        <v>187.32</v>
+      </c>
+      <c r="G738" t="n">
+        <v>166.35</v>
+      </c>
+      <c r="H738" t="n">
+        <v>158.15</v>
+      </c>
+      <c r="I738" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J738" t="b">
+        <v>0</v>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 171.11 &lt;= Upper 187.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>314.49</v>
+      </c>
+      <c r="E739" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="F739" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="G739" t="n">
+        <v>313.12</v>
+      </c>
+      <c r="H739" t="n">
+        <v>323.99</v>
+      </c>
+      <c r="I739" t="n">
+        <v>1</v>
+      </c>
+      <c r="J739" t="b">
+        <v>0</v>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 313.12 &lt;= EMA21 323.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>478.85</v>
+      </c>
+      <c r="E740" t="n">
+        <v>681.52</v>
+      </c>
+      <c r="F740" t="n">
+        <v>681.52</v>
+      </c>
+      <c r="G740" t="n">
+        <v>522.05</v>
+      </c>
+      <c r="H740" t="n">
+        <v>550.34</v>
+      </c>
+      <c r="I740" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J740" t="b">
+        <v>0</v>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 522.05 &lt;= EMA21 550.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>284.95</v>
+      </c>
+      <c r="E741" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="F741" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="G741" t="n">
+        <v>300.21</v>
+      </c>
+      <c r="H741" t="n">
+        <v>313.82</v>
+      </c>
+      <c r="I741" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J741" t="b">
+        <v>0</v>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 300.21 &lt;= EMA21 313.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>397.17</v>
+      </c>
+      <c r="E742" t="n">
+        <v>449.47</v>
+      </c>
+      <c r="F742" t="n">
+        <v>449.47</v>
+      </c>
+      <c r="G742" t="n">
+        <v>405.2</v>
+      </c>
+      <c r="H742" t="n">
+        <v>409.06</v>
+      </c>
+      <c r="I742" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J742" t="b">
+        <v>0</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 405.20 &lt;= EMA21 409.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>211.61</v>
+      </c>
+      <c r="E743" t="n">
+        <v>279.93</v>
+      </c>
+      <c r="F743" t="n">
+        <v>279.93</v>
+      </c>
+      <c r="G743" t="n">
+        <v>226.99</v>
+      </c>
+      <c r="H743" t="n">
+        <v>236.17</v>
+      </c>
+      <c r="I743" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J743" t="b">
+        <v>0</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 226.99 &lt;= EMA21 236.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>ANSS</t>
+        </is>
+      </c>
+      <c r="J744" t="b">
+        <v>0</v>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>128.71</v>
+      </c>
+      <c r="E745" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="F745" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="G745" t="n">
+        <v>140.24</v>
+      </c>
+      <c r="H745" t="n">
+        <v>143.88</v>
+      </c>
+      <c r="I745" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J745" t="b">
+        <v>0</v>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 140.24 &lt;= EMA21 143.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>TYL</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="E746" t="n">
+        <v>389.17</v>
+      </c>
+      <c r="F746" t="n">
+        <v>389.17</v>
+      </c>
+      <c r="G746" t="n">
+        <v>354.24</v>
+      </c>
+      <c r="H746" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="I746" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J746" t="b">
+        <v>0</v>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 335.48 &lt;= Upper 389.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>142.86</v>
+      </c>
+      <c r="E747" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="F747" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="G747" t="n">
+        <v>148.67</v>
+      </c>
+      <c r="H747" t="n">
+        <v>148.61</v>
+      </c>
+      <c r="I747" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J747" t="b">
+        <v>0</v>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 142.86 &lt;= Upper 161.67)</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>170.62</v>
+      </c>
+      <c r="E748" t="n">
+        <v>207.81</v>
+      </c>
+      <c r="F748" t="n">
+        <v>207.81</v>
+      </c>
+      <c r="G748" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="H748" t="n">
+        <v>182.76</v>
+      </c>
+      <c r="I748" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J748" t="b">
+        <v>0</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 181.48 &lt;= EMA21 182.76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="E749" t="n">
+        <v>66.31999999999999</v>
+      </c>
+      <c r="F749" t="n">
+        <v>66.31999999999999</v>
+      </c>
+      <c r="G749" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="H749" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="I749" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J749" t="b">
+        <v>0</v>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 58.32 &lt;= Upper 66.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="E750" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="F750" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="G750" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="H750" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="I750" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J750" t="b">
+        <v>0</v>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 11.47 &lt;= EMA21 11.71)</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="E751" t="n">
+        <v>123.83</v>
+      </c>
+      <c r="F751" t="n">
+        <v>123.83</v>
+      </c>
+      <c r="G751" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="H751" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="I751" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J751" t="b">
+        <v>0</v>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 114.52 &lt;= Upper 123.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="E752" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="F752" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="G752" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="H752" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="I752" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J752" t="b">
+        <v>0</v>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 29.97 &lt;= Upper 31.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="E753" t="n">
+        <v>156.45</v>
+      </c>
+      <c r="F753" t="n">
+        <v>156.45</v>
+      </c>
+      <c r="G753" t="n">
+        <v>145.73</v>
+      </c>
+      <c r="H753" t="n">
+        <v>143.79</v>
+      </c>
+      <c r="I753" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J753" t="b">
+        <v>0</v>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 142.60 &lt;= Upper 156.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>398.48</v>
+      </c>
+      <c r="E754" t="n">
+        <v>415.17</v>
+      </c>
+      <c r="F754" t="n">
+        <v>415.17</v>
+      </c>
+      <c r="G754" t="n">
+        <v>396.11</v>
+      </c>
+      <c r="H754" t="n">
+        <v>396.83</v>
+      </c>
+      <c r="I754" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J754" t="b">
+        <v>0</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 396.11 &lt;= EMA21 396.83)</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="J755" t="b">
+        <v>0</v>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>107.13</v>
+      </c>
+      <c r="E756" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="F756" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="G756" t="n">
+        <v>107.72</v>
+      </c>
+      <c r="H756" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="I756" t="n">
+        <v>1</v>
+      </c>
+      <c r="J756" t="b">
+        <v>0</v>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 107.72 &lt;= EMA21 110.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="J757" t="b">
+        <v>0</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>216.96</v>
+      </c>
+      <c r="E758" t="n">
+        <v>253.23</v>
+      </c>
+      <c r="F758" t="n">
+        <v>253.23</v>
+      </c>
+      <c r="G758" t="n">
+        <v>218.39</v>
+      </c>
+      <c r="H758" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="I758" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J758" t="b">
+        <v>0</v>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 218.39 &lt;= EMA21 226.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="E759" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="F759" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="G759" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="H759" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="I759" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J759" t="b">
+        <v>0</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 44.88 &lt;= Upper 45.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="E760" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="F760" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="G760" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="H760" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="I760" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J760" t="b">
+        <v>0</v>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 42.07 &lt;= Upper 48.43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="E761" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="F761" t="n">
+        <v>83.93000000000001</v>
+      </c>
+      <c r="G761" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="H761" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="I761" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J761" t="b">
+        <v>0</v>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 76.01 &lt;= Upper 83.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>105.82</v>
+      </c>
+      <c r="E762" t="n">
+        <v>111.04</v>
+      </c>
+      <c r="F762" t="n">
+        <v>111.04</v>
+      </c>
+      <c r="G762" t="n">
+        <v>106.07</v>
+      </c>
+      <c r="H762" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="I762" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J762" t="b">
+        <v>0</v>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 105.82 &lt;= Upper 111.04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E763" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="F763" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="G763" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="H763" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I763" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J763" t="b">
+        <v>0</v>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 28.20 &lt;= Upper 29.04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>PARA</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E764" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F764" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G764" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H764" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I764" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J764" t="b">
+        <v>0</v>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1.08 &lt;= EMA21 1.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>521.73</v>
+      </c>
+      <c r="E765" t="n">
+        <v>569.85</v>
+      </c>
+      <c r="F765" t="n">
+        <v>569.85</v>
+      </c>
+      <c r="G765" t="n">
+        <v>534.74</v>
+      </c>
+      <c r="H765" t="n">
+        <v>529.3099999999999</v>
+      </c>
+      <c r="I765" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J765" t="b">
+        <v>0</v>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 521.73 &lt;= Upper 569.85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>TME</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E766" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="F766" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="G766" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="H766" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="I766" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J766" t="b">
+        <v>0</v>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 8.19 &lt;= EMA21 8.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="E767" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="F767" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="G767" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="H767" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="I767" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J767" t="b">
+        <v>0</v>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 106.20 &lt;= EMA21 107.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>902.38</v>
+      </c>
+      <c r="E768" t="n">
+        <v>982.42</v>
+      </c>
+      <c r="F768" t="n">
+        <v>982.42</v>
+      </c>
+      <c r="G768" t="n">
+        <v>920.13</v>
+      </c>
+      <c r="H768" t="n">
+        <v>933.16</v>
+      </c>
+      <c r="I768" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J768" t="b">
+        <v>0</v>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 920.13 &lt;= EMA21 933.16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>155.73</v>
+      </c>
+      <c r="E769" t="n">
+        <v>170.76</v>
+      </c>
+      <c r="F769" t="n">
+        <v>170.76</v>
+      </c>
+      <c r="G769" t="n">
+        <v>160.67</v>
+      </c>
+      <c r="H769" t="n">
+        <v>158.7</v>
+      </c>
+      <c r="I769" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J769" t="b">
+        <v>0</v>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 155.73 &lt;= Upper 170.76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>305.69</v>
+      </c>
+      <c r="E770" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="F770" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="G770" t="n">
+        <v>316.72</v>
+      </c>
+      <c r="H770" t="n">
+        <v>324.56</v>
+      </c>
+      <c r="I770" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J770" t="b">
+        <v>0</v>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 316.72 &lt;= EMA21 324.56)</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>196.59</v>
+      </c>
+      <c r="E771" t="n">
+        <v>225.09</v>
+      </c>
+      <c r="F771" t="n">
+        <v>225.09</v>
+      </c>
+      <c r="G771" t="n">
+        <v>202.1</v>
+      </c>
+      <c r="H771" t="n">
+        <v>206.88</v>
+      </c>
+      <c r="I771" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J771" t="b">
+        <v>0</v>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 202.10 &lt;= EMA21 206.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="E772" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="F772" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G772" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="H772" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="I772" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J772" t="b">
+        <v>0</v>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 57.46 &lt;= EMA21 57.48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E773" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="F773" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="G773" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="H773" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="I773" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J773" t="b">
+        <v>0</v>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 12.17 &lt;= EMA21 12.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="E774" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F774" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="G774" t="n">
+        <v>126.74</v>
+      </c>
+      <c r="H774" t="n">
+        <v>125.72</v>
+      </c>
+      <c r="I774" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J774" t="b">
+        <v>0</v>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 122.99 &lt;= Upper 132.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>118.66</v>
+      </c>
+      <c r="E775" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="F775" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="G775" t="n">
+        <v>125.49</v>
+      </c>
+      <c r="H775" t="n">
+        <v>127.53</v>
+      </c>
+      <c r="I775" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J775" t="b">
+        <v>0</v>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 125.49 &lt;= EMA21 127.53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>BJ</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="E776" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="F776" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="G776" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="H776" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="I776" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J776" t="b">
+        <v>0</v>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 91.06 &lt;= EMA21 92.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>225.48</v>
+      </c>
+      <c r="E777" t="n">
+        <v>245.36</v>
+      </c>
+      <c r="F777" t="n">
+        <v>245.36</v>
+      </c>
+      <c r="G777" t="n">
+        <v>229.14</v>
+      </c>
+      <c r="H777" t="n">
+        <v>233</v>
+      </c>
+      <c r="I777" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J777" t="b">
+        <v>0</v>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 229.14 &lt;= EMA21 233.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>126.42</v>
+      </c>
+      <c r="E778" t="n">
+        <v>155.23</v>
+      </c>
+      <c r="F778" t="n">
+        <v>155.23</v>
+      </c>
+      <c r="G778" t="n">
+        <v>131.06</v>
+      </c>
+      <c r="H778" t="n">
+        <v>137.52</v>
+      </c>
+      <c r="I778" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J778" t="b">
+        <v>0</v>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 131.06 &lt;= EMA21 137.52)</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="E779" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="F779" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G779" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="H779" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I779" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J779" t="b">
+        <v>0</v>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 38.01 &lt;= EMA21 38.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="E780" t="n">
+        <v>131.34</v>
+      </c>
+      <c r="F780" t="n">
+        <v>131.34</v>
+      </c>
+      <c r="G780" t="n">
+        <v>107.86</v>
+      </c>
+      <c r="H780" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="I780" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J780" t="b">
+        <v>0</v>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 107.86 &lt;= EMA21 113.39)</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="E781" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="F781" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="G781" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="H781" t="n">
+        <v>104.61</v>
+      </c>
+      <c r="I781" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J781" t="b">
+        <v>0</v>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 103.24 &lt;= EMA21 104.61)</t>
         </is>
       </c>
     </row>
@@ -29418,7 +33664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29794,6 +34040,99 @@
         <v>1.43</v>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>168.92</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="E15" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -29873,34 +34212,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>174.09</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1914.99</v>
+        <v>1961.07</v>
       </c>
       <c r="F2" t="n">
-        <v>174.09</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>166.26</v>
+        <v>624.27</v>
       </c>
       <c r="I2" t="n">
-        <v>174.09</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -29914,34 +34253,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>162.52</v>
+        <v>112.36</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>1950.24</v>
+        <v>1910.12</v>
       </c>
       <c r="F3" t="n">
-        <v>162.52</v>
+        <v>112.36</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>155.21</v>
+        <v>107.3</v>
       </c>
       <c r="I3" t="n">
-        <v>162.52</v>
+        <v>112.36</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -29955,34 +34294,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>104.07</v>
+        <v>84.03</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>1977.33</v>
+        <v>1932.69</v>
       </c>
       <c r="F4" t="n">
-        <v>104.07</v>
+        <v>84.03</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>99.39</v>
+        <v>80.25</v>
       </c>
       <c r="I4" t="n">
-        <v>104.07</v>
+        <v>84.03</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -29996,34 +34335,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>653.6900000000001</v>
+        <v>176.88</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>1961.07</v>
+        <v>1945.68</v>
       </c>
       <c r="F5" t="n">
-        <v>653.6900000000001</v>
+        <v>176.88</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>624.27</v>
+        <v>168.92</v>
       </c>
       <c r="I5" t="n">
-        <v>653.6900000000001</v>
+        <v>176.88</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -30045,7 +34384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30263,6 +34602,159 @@
         <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>174.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>172.13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1914.99</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.126</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.176</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-22.52</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>TRAILING_STOP</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>162.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1950.24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-4.498</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-4.548</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-88.7</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>HARD_STOP_LOSS</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1977.33</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>TRAILING_STOP</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -30279,7 +34771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30775,6 +35267,300 @@
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8B10B16FF4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>172.13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>172.13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TRAILING_STOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4AFB31A78F</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="G12" t="n">
+        <v>155.21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>HARD_STOP_LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7753B8F48D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TRAILING_STOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2D3CA7BB7B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="G14" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>17</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>71E174183A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="G15" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>23</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F7496823D2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="G16" t="n">
+        <v>176.88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Entry Breakout</t>
         </is>
@@ -30791,7 +35577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30845,6 +35631,60 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>No bar data available for today 2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GAP_DOWN_SLIP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Opened at 172.13 below SL of 174.19. Filled at Open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:39:18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GAP_DOWN_SLIP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Opened at 104.36 below SL of 109.14. Filled at Open.</t>
         </is>
       </c>
     </row>
@@ -30859,7 +35699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31272,6 +36112,39 @@
         <v>4</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>04:39:23</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2012.32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7749.56</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9761.879999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-238.12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K781"/>
+  <dimension ref="A1:K881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33650,6 +33650,4234 @@
       <c r="K781" t="inlineStr">
         <is>
           <t>EMA_BEARISH (EMA9 103.24 &lt;= EMA21 104.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="J782" t="b">
+        <v>0</v>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D783" t="n">
+        <v>495.63</v>
+      </c>
+      <c r="E783" t="n">
+        <v>514.13</v>
+      </c>
+      <c r="F783" t="n">
+        <v>514.13</v>
+      </c>
+      <c r="G783" t="n">
+        <v>496.43</v>
+      </c>
+      <c r="H783" t="n">
+        <v>490.21</v>
+      </c>
+      <c r="I783" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J783" t="b">
+        <v>0</v>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 495.63 &lt;= Upper 514.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D784" t="n">
+        <v>218.29</v>
+      </c>
+      <c r="E784" t="n">
+        <v>232.14</v>
+      </c>
+      <c r="F784" t="n">
+        <v>232.14</v>
+      </c>
+      <c r="G784" t="n">
+        <v>221.48</v>
+      </c>
+      <c r="H784" t="n">
+        <v>219.52</v>
+      </c>
+      <c r="I784" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J784" t="b">
+        <v>0</v>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 218.29 &lt;= Upper 232.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D785" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="E785" t="n">
+        <v>350.41</v>
+      </c>
+      <c r="F785" t="n">
+        <v>350.41</v>
+      </c>
+      <c r="G785" t="n">
+        <v>337.39</v>
+      </c>
+      <c r="H785" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="I785" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J785" t="b">
+        <v>0</v>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 337.39 &lt;= EMA21 340.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D786" t="n">
+        <v>335.45</v>
+      </c>
+      <c r="E786" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="F786" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="G786" t="n">
+        <v>334.51</v>
+      </c>
+      <c r="H786" t="n">
+        <v>338.01</v>
+      </c>
+      <c r="I786" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J786" t="b">
+        <v>0</v>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 334.51 &lt;= EMA21 338.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D787" t="n">
+        <v>256.78</v>
+      </c>
+      <c r="E787" t="n">
+        <v>266.66</v>
+      </c>
+      <c r="F787" t="n">
+        <v>266.66</v>
+      </c>
+      <c r="G787" t="n">
+        <v>256.35</v>
+      </c>
+      <c r="H787" t="n">
+        <v>257.94</v>
+      </c>
+      <c r="I787" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J787" t="b">
+        <v>0</v>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 256.35 &lt;= EMA21 257.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D788" t="n">
+        <v>648.03</v>
+      </c>
+      <c r="E788" t="n">
+        <v>655.15</v>
+      </c>
+      <c r="F788" t="n">
+        <v>655.15</v>
+      </c>
+      <c r="G788" t="n">
+        <v>620.72</v>
+      </c>
+      <c r="H788" t="n">
+        <v>601.79</v>
+      </c>
+      <c r="I788" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J788" t="b">
+        <v>0</v>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 648.03 &lt;= Upper 655.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D789" t="n">
+        <v>365.44</v>
+      </c>
+      <c r="E789" t="n">
+        <v>376.86</v>
+      </c>
+      <c r="F789" t="n">
+        <v>376.86</v>
+      </c>
+      <c r="G789" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="H789" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="I789" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J789" t="b">
+        <v>0</v>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 365.44 &lt;= Upper 376.86)</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D790" t="n">
+        <v>361.99</v>
+      </c>
+      <c r="E790" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="F790" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="G790" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="H790" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="I790" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J790" t="b">
+        <v>0</v>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 364.13 &lt;= EMA21 370.81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D791" t="n">
+        <v>150.28</v>
+      </c>
+      <c r="E791" t="n">
+        <v>161.93</v>
+      </c>
+      <c r="F791" t="n">
+        <v>161.93</v>
+      </c>
+      <c r="G791" t="n">
+        <v>153.35</v>
+      </c>
+      <c r="H791" t="n">
+        <v>150.03</v>
+      </c>
+      <c r="I791" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J791" t="b">
+        <v>0</v>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 150.28 &lt;= Upper 161.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D792" t="n">
+        <v>247.72</v>
+      </c>
+      <c r="E792" t="n">
+        <v>284.07</v>
+      </c>
+      <c r="F792" t="n">
+        <v>284.07</v>
+      </c>
+      <c r="G792" t="n">
+        <v>246.44</v>
+      </c>
+      <c r="H792" t="n">
+        <v>232.44</v>
+      </c>
+      <c r="I792" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J792" t="b">
+        <v>0</v>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 247.72 &lt;= Upper 284.07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D793" t="n">
+        <v>252.23</v>
+      </c>
+      <c r="E793" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="F793" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="G793" t="n">
+        <v>263.56</v>
+      </c>
+      <c r="H793" t="n">
+        <v>266.24</v>
+      </c>
+      <c r="I793" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J793" t="b">
+        <v>0</v>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 263.56 &lt;= EMA21 266.24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D794" t="n">
+        <v>516.13</v>
+      </c>
+      <c r="E794" t="n">
+        <v>524.87</v>
+      </c>
+      <c r="F794" t="n">
+        <v>524.87</v>
+      </c>
+      <c r="G794" t="n">
+        <v>494.1</v>
+      </c>
+      <c r="H794" t="n">
+        <v>487.01</v>
+      </c>
+      <c r="I794" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J794" t="b">
+        <v>0</v>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 516.13 &lt;= Upper 524.87)</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="D795" t="n">
+        <v>102.94</v>
+      </c>
+      <c r="E795" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F795" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="G795" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="H795" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="I795" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J795" t="b">
+        <v>0</v>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 102.94 &lt;= Upper 107.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D796" t="n">
+        <v>975.26</v>
+      </c>
+      <c r="E796" t="n">
+        <v>1026.84</v>
+      </c>
+      <c r="F796" t="n">
+        <v>1026.84</v>
+      </c>
+      <c r="G796" t="n">
+        <v>978.64</v>
+      </c>
+      <c r="H796" t="n">
+        <v>959.4400000000001</v>
+      </c>
+      <c r="I796" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J796" t="b">
+        <v>0</v>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 975.26 &lt;= Upper 1026.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D797" t="n">
+        <v>181.97</v>
+      </c>
+      <c r="E797" t="n">
+        <v>179.85</v>
+      </c>
+      <c r="F797" t="n">
+        <v>179.85</v>
+      </c>
+      <c r="G797" t="n">
+        <v>173.18</v>
+      </c>
+      <c r="H797" t="n">
+        <v>168.95</v>
+      </c>
+      <c r="I797" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J797" t="b">
+        <v>0</v>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.05x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="E798" t="n">
+        <v>279.13</v>
+      </c>
+      <c r="F798" t="n">
+        <v>279.13</v>
+      </c>
+      <c r="G798" t="n">
+        <v>261.24</v>
+      </c>
+      <c r="H798" t="n">
+        <v>264.45</v>
+      </c>
+      <c r="I798" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J798" t="b">
+        <v>0</v>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 261.24 &lt;= EMA21 264.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>456.49</v>
+      </c>
+      <c r="E799" t="n">
+        <v>527.9299999999999</v>
+      </c>
+      <c r="F799" t="n">
+        <v>527.9299999999999</v>
+      </c>
+      <c r="G799" t="n">
+        <v>460.43</v>
+      </c>
+      <c r="H799" t="n">
+        <v>475.94</v>
+      </c>
+      <c r="I799" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J799" t="b">
+        <v>0</v>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 460.43 &lt;= EMA21 475.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>298.22</v>
+      </c>
+      <c r="E800" t="n">
+        <v>338.71</v>
+      </c>
+      <c r="F800" t="n">
+        <v>338.71</v>
+      </c>
+      <c r="G800" t="n">
+        <v>304.39</v>
+      </c>
+      <c r="H800" t="n">
+        <v>307.79</v>
+      </c>
+      <c r="I800" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J800" t="b">
+        <v>0</v>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 304.39 &lt;= EMA21 307.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
+        <v>180.64</v>
+      </c>
+      <c r="E801" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="F801" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="G801" t="n">
+        <v>180.69</v>
+      </c>
+      <c r="H801" t="n">
+        <v>184.64</v>
+      </c>
+      <c r="I801" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J801" t="b">
+        <v>0</v>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 180.69 &lt;= EMA21 184.64)</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D802" t="n">
+        <v>1698.3</v>
+      </c>
+      <c r="E802" t="n">
+        <v>1852.66</v>
+      </c>
+      <c r="F802" t="n">
+        <v>1852.66</v>
+      </c>
+      <c r="G802" t="n">
+        <v>1709.16</v>
+      </c>
+      <c r="H802" t="n">
+        <v>1722.07</v>
+      </c>
+      <c r="I802" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J802" t="b">
+        <v>0</v>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1709.16 &lt;= EMA21 1722.07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="D803" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="E803" t="n">
+        <v>388</v>
+      </c>
+      <c r="F803" t="n">
+        <v>388</v>
+      </c>
+      <c r="G803" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="H803" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="I803" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J803" t="b">
+        <v>0</v>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 365.96 &lt;= EMA21 368.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="D804" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="E804" t="n">
+        <v>253.8</v>
+      </c>
+      <c r="F804" t="n">
+        <v>253.8</v>
+      </c>
+      <c r="G804" t="n">
+        <v>226.57</v>
+      </c>
+      <c r="H804" t="n">
+        <v>224.15</v>
+      </c>
+      <c r="I804" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J804" t="b">
+        <v>0</v>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 236.10 &lt;= Upper 253.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="D805" t="n">
+        <v>236.62</v>
+      </c>
+      <c r="E805" t="n">
+        <v>234.54</v>
+      </c>
+      <c r="F805" t="n">
+        <v>234.54</v>
+      </c>
+      <c r="G805" t="n">
+        <v>227.64</v>
+      </c>
+      <c r="H805" t="n">
+        <v>229.77</v>
+      </c>
+      <c r="I805" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J805" t="b">
+        <v>0</v>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 227.64 &lt;= EMA21 229.77)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D806" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="E806" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="F806" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="G806" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="H806" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="I806" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J806" t="b">
+        <v>0</v>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.11 &lt;= EMA21 75.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>1234.46</v>
+      </c>
+      <c r="E807" t="n">
+        <v>1403.2</v>
+      </c>
+      <c r="F807" t="n">
+        <v>1403.2</v>
+      </c>
+      <c r="G807" t="n">
+        <v>1228.68</v>
+      </c>
+      <c r="H807" t="n">
+        <v>1266.58</v>
+      </c>
+      <c r="I807" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J807" t="b">
+        <v>0</v>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1228.68 &lt;= EMA21 1266.58)</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="E808" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="F808" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="G808" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="H808" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="I808" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J808" t="b">
+        <v>1</v>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="E809" t="n">
+        <v>111.63</v>
+      </c>
+      <c r="F809" t="n">
+        <v>111.63</v>
+      </c>
+      <c r="G809" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="H809" t="n">
+        <v>100.92</v>
+      </c>
+      <c r="I809" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J809" t="b">
+        <v>1</v>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="E810" t="n">
+        <v>425.35</v>
+      </c>
+      <c r="F810" t="n">
+        <v>425.35</v>
+      </c>
+      <c r="G810" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="H810" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="I810" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J810" t="b">
+        <v>0</v>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 367.51 &lt;= EMA21 368.52)</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>ENTG</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>140.37</v>
+      </c>
+      <c r="E811" t="n">
+        <v>159.41</v>
+      </c>
+      <c r="F811" t="n">
+        <v>159.41</v>
+      </c>
+      <c r="G811" t="n">
+        <v>138.76</v>
+      </c>
+      <c r="H811" t="n">
+        <v>139.93</v>
+      </c>
+      <c r="I811" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J811" t="b">
+        <v>0</v>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 138.76 &lt;= EMA21 139.93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D812" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="E812" t="n">
+        <v>79.02</v>
+      </c>
+      <c r="F812" t="n">
+        <v>79.02</v>
+      </c>
+      <c r="G812" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="H812" t="n">
+        <v>74.66</v>
+      </c>
+      <c r="I812" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J812" t="b">
+        <v>0</v>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 73.37 &lt;= EMA21 74.66)</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D813" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E813" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="F813" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="G813" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="H813" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="I813" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J813" t="b">
+        <v>0</v>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 40.10 &lt;= Upper 40.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D814" t="n">
+        <v>567.29</v>
+      </c>
+      <c r="E814" t="n">
+        <v>559.79</v>
+      </c>
+      <c r="F814" t="n">
+        <v>559.79</v>
+      </c>
+      <c r="G814" t="n">
+        <v>514.6900000000001</v>
+      </c>
+      <c r="H814" t="n">
+        <v>487.27</v>
+      </c>
+      <c r="I814" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J814" t="b">
+        <v>1</v>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D815" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="E815" t="n">
+        <v>34</v>
+      </c>
+      <c r="F815" t="n">
+        <v>34</v>
+      </c>
+      <c r="G815" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="H815" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I815" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J815" t="b">
+        <v>1</v>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>QUALIFIED_BREAKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="D816" t="n">
+        <v>447.18</v>
+      </c>
+      <c r="E816" t="n">
+        <v>514.9</v>
+      </c>
+      <c r="F816" t="n">
+        <v>514.9</v>
+      </c>
+      <c r="G816" t="n">
+        <v>460.84</v>
+      </c>
+      <c r="H816" t="n">
+        <v>467.52</v>
+      </c>
+      <c r="I816" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J816" t="b">
+        <v>0</v>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 460.84 &lt;= EMA21 467.52)</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D817" t="n">
+        <v>830.17</v>
+      </c>
+      <c r="E817" t="n">
+        <v>962.65</v>
+      </c>
+      <c r="F817" t="n">
+        <v>962.65</v>
+      </c>
+      <c r="G817" t="n">
+        <v>849.84</v>
+      </c>
+      <c r="H817" t="n">
+        <v>849.6</v>
+      </c>
+      <c r="I817" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J817" t="b">
+        <v>0</v>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 830.17 &lt;= Upper 962.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D818" t="n">
+        <v>199.59</v>
+      </c>
+      <c r="E818" t="n">
+        <v>204.19</v>
+      </c>
+      <c r="F818" t="n">
+        <v>204.19</v>
+      </c>
+      <c r="G818" t="n">
+        <v>193.65</v>
+      </c>
+      <c r="H818" t="n">
+        <v>192.18</v>
+      </c>
+      <c r="I818" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J818" t="b">
+        <v>0</v>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 199.59 &lt;= Upper 204.19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D819" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="E819" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="F819" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="G819" t="n">
+        <v>109.92</v>
+      </c>
+      <c r="H819" t="n">
+        <v>111.19</v>
+      </c>
+      <c r="I819" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J819" t="b">
+        <v>0</v>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 109.92 &lt;= EMA21 111.19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="D820" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="E820" t="n">
+        <v>195.42</v>
+      </c>
+      <c r="F820" t="n">
+        <v>195.42</v>
+      </c>
+      <c r="G820" t="n">
+        <v>182.83</v>
+      </c>
+      <c r="H820" t="n">
+        <v>180.81</v>
+      </c>
+      <c r="I820" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J820" t="b">
+        <v>0</v>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 183.90 &lt;= Upper 195.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D821" t="n">
+        <v>243.29</v>
+      </c>
+      <c r="E821" t="n">
+        <v>241.32</v>
+      </c>
+      <c r="F821" t="n">
+        <v>241.32</v>
+      </c>
+      <c r="G821" t="n">
+        <v>236.36</v>
+      </c>
+      <c r="H821" t="n">
+        <v>235.04</v>
+      </c>
+      <c r="I821" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J821" t="b">
+        <v>0</v>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 1.02x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D822" t="n">
+        <v>132.53</v>
+      </c>
+      <c r="E822" t="n">
+        <v>149.94</v>
+      </c>
+      <c r="F822" t="n">
+        <v>149.94</v>
+      </c>
+      <c r="G822" t="n">
+        <v>134.92</v>
+      </c>
+      <c r="H822" t="n">
+        <v>131.87</v>
+      </c>
+      <c r="I822" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J822" t="b">
+        <v>0</v>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 132.53 &lt;= Upper 149.94)</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D823" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="E823" t="n">
+        <v>379.45</v>
+      </c>
+      <c r="F823" t="n">
+        <v>379.45</v>
+      </c>
+      <c r="G823" t="n">
+        <v>328.97</v>
+      </c>
+      <c r="H823" t="n">
+        <v>334.63</v>
+      </c>
+      <c r="I823" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J823" t="b">
+        <v>0</v>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 328.97 &lt;= EMA21 334.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D824" t="n">
+        <v>330.65</v>
+      </c>
+      <c r="E824" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="F824" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="G824" t="n">
+        <v>340.61</v>
+      </c>
+      <c r="H824" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="I824" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J824" t="b">
+        <v>0</v>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 340.61 &lt;= EMA21 347.90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D825" t="n">
+        <v>206.74</v>
+      </c>
+      <c r="E825" t="n">
+        <v>233.05</v>
+      </c>
+      <c r="F825" t="n">
+        <v>233.05</v>
+      </c>
+      <c r="G825" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="H825" t="n">
+        <v>208.16</v>
+      </c>
+      <c r="I825" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J825" t="b">
+        <v>0</v>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 206.74 &lt;= Upper 233.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="D826" t="n">
+        <v>328.99</v>
+      </c>
+      <c r="E826" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="F826" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="G826" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="H826" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="I826" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J826" t="b">
+        <v>0</v>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 328.99 &lt;= Upper 347.77)</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D827" t="n">
+        <v>167.23</v>
+      </c>
+      <c r="E827" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="F827" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="G827" t="n">
+        <v>171.98</v>
+      </c>
+      <c r="H827" t="n">
+        <v>170.73</v>
+      </c>
+      <c r="I827" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J827" t="b">
+        <v>0</v>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 167.23 &lt;= Upper 187.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="D828" t="n">
+        <v>221.21</v>
+      </c>
+      <c r="E828" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="F828" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="G828" t="n">
+        <v>221.61</v>
+      </c>
+      <c r="H828" t="n">
+        <v>229.02</v>
+      </c>
+      <c r="I828" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J828" t="b">
+        <v>0</v>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 221.61 &lt;= EMA21 229.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="D829" t="n">
+        <v>164.54</v>
+      </c>
+      <c r="E829" t="n">
+        <v>193.46</v>
+      </c>
+      <c r="F829" t="n">
+        <v>193.46</v>
+      </c>
+      <c r="G829" t="n">
+        <v>169.35</v>
+      </c>
+      <c r="H829" t="n">
+        <v>171.24</v>
+      </c>
+      <c r="I829" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J829" t="b">
+        <v>0</v>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 169.35 &lt;= EMA21 171.24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="D830" t="n">
+        <v>306.53</v>
+      </c>
+      <c r="E830" t="n">
+        <v>321.72</v>
+      </c>
+      <c r="F830" t="n">
+        <v>321.72</v>
+      </c>
+      <c r="G830" t="n">
+        <v>297.95</v>
+      </c>
+      <c r="H830" t="n">
+        <v>294</v>
+      </c>
+      <c r="I830" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J830" t="b">
+        <v>0</v>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 306.53 &lt;= Upper 321.72)</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="D831" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="E831" t="n">
+        <v>479.22</v>
+      </c>
+      <c r="F831" t="n">
+        <v>479.22</v>
+      </c>
+      <c r="G831" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="H831" t="n">
+        <v>392.25</v>
+      </c>
+      <c r="I831" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J831" t="b">
+        <v>0</v>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 380.35 &lt;= EMA21 392.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D832" t="n">
+        <v>156.07</v>
+      </c>
+      <c r="E832" t="n">
+        <v>169.82</v>
+      </c>
+      <c r="F832" t="n">
+        <v>169.82</v>
+      </c>
+      <c r="G832" t="n">
+        <v>158.09</v>
+      </c>
+      <c r="H832" t="n">
+        <v>158.56</v>
+      </c>
+      <c r="I832" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J832" t="b">
+        <v>0</v>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 158.09 &lt;= EMA21 158.56)</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D833" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="E833" t="n">
+        <v>199.3</v>
+      </c>
+      <c r="F833" t="n">
+        <v>199.3</v>
+      </c>
+      <c r="G833" t="n">
+        <v>181.18</v>
+      </c>
+      <c r="H833" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="I833" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J833" t="b">
+        <v>0</v>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 179.70 &lt;= Upper 199.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="D834" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="E834" t="n">
+        <v>207.69</v>
+      </c>
+      <c r="F834" t="n">
+        <v>207.69</v>
+      </c>
+      <c r="G834" t="n">
+        <v>190.97</v>
+      </c>
+      <c r="H834" t="n">
+        <v>189.38</v>
+      </c>
+      <c r="I834" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J834" t="b">
+        <v>0</v>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 185.70 &lt;= Upper 207.69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D835" t="n">
+        <v>225.33</v>
+      </c>
+      <c r="E835" t="n">
+        <v>266.28</v>
+      </c>
+      <c r="F835" t="n">
+        <v>266.28</v>
+      </c>
+      <c r="G835" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="H835" t="n">
+        <v>237.38</v>
+      </c>
+      <c r="I835" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J835" t="b">
+        <v>0</v>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 236.80 &lt;= EMA21 237.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="D836" t="n">
+        <v>262.4</v>
+      </c>
+      <c r="E836" t="n">
+        <v>293.57</v>
+      </c>
+      <c r="F836" t="n">
+        <v>293.57</v>
+      </c>
+      <c r="G836" t="n">
+        <v>266.41</v>
+      </c>
+      <c r="H836" t="n">
+        <v>257.91</v>
+      </c>
+      <c r="I836" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J836" t="b">
+        <v>0</v>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 262.40 &lt;= Upper 293.57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="D837" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="E837" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="F837" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="G837" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="H837" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="I837" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J837" t="b">
+        <v>0</v>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 97.15 &lt;= EMA21 98.52)</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="D838" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="E838" t="n">
+        <v>188.33</v>
+      </c>
+      <c r="F838" t="n">
+        <v>188.33</v>
+      </c>
+      <c r="G838" t="n">
+        <v>166.38</v>
+      </c>
+      <c r="H838" t="n">
+        <v>158.91</v>
+      </c>
+      <c r="I838" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J838" t="b">
+        <v>0</v>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 166.50 &lt;= Upper 188.33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="D839" t="n">
+        <v>323.96</v>
+      </c>
+      <c r="E839" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="F839" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="G839" t="n">
+        <v>315.29</v>
+      </c>
+      <c r="H839" t="n">
+        <v>323.99</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J839" t="b">
+        <v>0</v>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 315.29 &lt;= EMA21 323.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="D840" t="n">
+        <v>479.34</v>
+      </c>
+      <c r="E840" t="n">
+        <v>680.87</v>
+      </c>
+      <c r="F840" t="n">
+        <v>680.87</v>
+      </c>
+      <c r="G840" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="H840" t="n">
+        <v>543.88</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J840" t="b">
+        <v>0</v>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 513.50 &lt;= EMA21 543.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="D841" t="n">
+        <v>289.37</v>
+      </c>
+      <c r="E841" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="F841" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="G841" t="n">
+        <v>298.04</v>
+      </c>
+      <c r="H841" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="I841" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J841" t="b">
+        <v>0</v>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 298.04 &lt;= EMA21 311.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="D842" t="n">
+        <v>397.38</v>
+      </c>
+      <c r="E842" t="n">
+        <v>449.28</v>
+      </c>
+      <c r="F842" t="n">
+        <v>449.28</v>
+      </c>
+      <c r="G842" t="n">
+        <v>403.64</v>
+      </c>
+      <c r="H842" t="n">
+        <v>407.99</v>
+      </c>
+      <c r="I842" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J842" t="b">
+        <v>0</v>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 403.64 &lt;= EMA21 407.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D843" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="E843" t="n">
+        <v>279.64</v>
+      </c>
+      <c r="F843" t="n">
+        <v>279.64</v>
+      </c>
+      <c r="G843" t="n">
+        <v>224.07</v>
+      </c>
+      <c r="H843" t="n">
+        <v>234.01</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J843" t="b">
+        <v>0</v>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 224.07 &lt;= EMA21 234.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>ANSS</t>
+        </is>
+      </c>
+      <c r="J844" t="b">
+        <v>0</v>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="D845" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="E845" t="n">
+        <v>166.51</v>
+      </c>
+      <c r="F845" t="n">
+        <v>166.51</v>
+      </c>
+      <c r="G845" t="n">
+        <v>138.35</v>
+      </c>
+      <c r="H845" t="n">
+        <v>142.69</v>
+      </c>
+      <c r="I845" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J845" t="b">
+        <v>0</v>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 138.35 &lt;= EMA21 142.69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>TYL</t>
+        </is>
+      </c>
+      <c r="D846" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="E846" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="F846" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="G846" t="n">
+        <v>350.72</v>
+      </c>
+      <c r="H846" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J846" t="b">
+        <v>0</v>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 336.67 &lt;= Upper 388.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D847" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="E847" t="n">
+        <v>161.97</v>
+      </c>
+      <c r="F847" t="n">
+        <v>161.97</v>
+      </c>
+      <c r="G847" t="n">
+        <v>147.27</v>
+      </c>
+      <c r="H847" t="n">
+        <v>147.98</v>
+      </c>
+      <c r="I847" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J847" t="b">
+        <v>0</v>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 147.27 &lt;= EMA21 147.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D848" t="n">
+        <v>179.59</v>
+      </c>
+      <c r="E848" t="n">
+        <v>207.89</v>
+      </c>
+      <c r="F848" t="n">
+        <v>207.89</v>
+      </c>
+      <c r="G848" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="H848" t="n">
+        <v>182.47</v>
+      </c>
+      <c r="I848" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J848" t="b">
+        <v>0</v>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 181.10 &lt;= EMA21 182.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="D849" t="n">
+        <v>60</v>
+      </c>
+      <c r="E849" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="F849" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="G849" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="H849" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="I849" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J849" t="b">
+        <v>0</v>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 60.00 &lt;= Upper 66.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D850" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="E850" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="F850" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="G850" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="H850" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="I850" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J850" t="b">
+        <v>0</v>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 11.39 &lt;= EMA21 11.65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D851" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="E851" t="n">
+        <v>124.21</v>
+      </c>
+      <c r="F851" t="n">
+        <v>124.21</v>
+      </c>
+      <c r="G851" t="n">
+        <v>115.54</v>
+      </c>
+      <c r="H851" t="n">
+        <v>111.74</v>
+      </c>
+      <c r="I851" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J851" t="b">
+        <v>0</v>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 117.91 &lt;= Upper 124.21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="D852" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="E852" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="F852" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="G852" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="H852" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="I852" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J852" t="b">
+        <v>0</v>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 30.26 &lt;= Upper 31.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D853" t="n">
+        <v>153.79</v>
+      </c>
+      <c r="E853" t="n">
+        <v>157.92</v>
+      </c>
+      <c r="F853" t="n">
+        <v>157.92</v>
+      </c>
+      <c r="G853" t="n">
+        <v>147.34</v>
+      </c>
+      <c r="H853" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="I853" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J853" t="b">
+        <v>0</v>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 153.79 &lt;= Upper 157.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D854" t="n">
+        <v>411.71</v>
+      </c>
+      <c r="E854" t="n">
+        <v>414.09</v>
+      </c>
+      <c r="F854" t="n">
+        <v>414.09</v>
+      </c>
+      <c r="G854" t="n">
+        <v>399.23</v>
+      </c>
+      <c r="H854" t="n">
+        <v>398.18</v>
+      </c>
+      <c r="I854" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J854" t="b">
+        <v>0</v>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 411.71 &lt;= Upper 414.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="J855" t="b">
+        <v>0</v>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="D856" t="n">
+        <v>106.79</v>
+      </c>
+      <c r="E856" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="F856" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="G856" t="n">
+        <v>107.53</v>
+      </c>
+      <c r="H856" t="n">
+        <v>109.86</v>
+      </c>
+      <c r="I856" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J856" t="b">
+        <v>0</v>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 107.53 &lt;= EMA21 109.86)</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="J857" t="b">
+        <v>0</v>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_DATA (&lt; 30 bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="D858" t="n">
+        <v>215.47</v>
+      </c>
+      <c r="E858" t="n">
+        <v>251.84</v>
+      </c>
+      <c r="F858" t="n">
+        <v>251.84</v>
+      </c>
+      <c r="G858" t="n">
+        <v>217.81</v>
+      </c>
+      <c r="H858" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="I858" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J858" t="b">
+        <v>0</v>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 217.81 &lt;= EMA21 225.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="D859" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E859" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="F859" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="G859" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="H859" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="I859" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J859" t="b">
+        <v>0</v>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 45.50 &lt;= Upper 45.96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="E860" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="F860" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="G860" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="H860" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="I860" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J860" t="b">
+        <v>0</v>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 43.96 &lt;= Upper 48.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="E861" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="F861" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="G861" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="H861" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="I861" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J861" t="b">
+        <v>0</v>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 78.26 &lt;= EMA21 78.32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="E862" t="n">
+        <v>111.02</v>
+      </c>
+      <c r="F862" t="n">
+        <v>111.02</v>
+      </c>
+      <c r="G862" t="n">
+        <v>106.17</v>
+      </c>
+      <c r="H862" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="I862" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J862" t="b">
+        <v>0</v>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 106.55 &lt;= Upper 111.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="E863" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="F863" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="G863" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="H863" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="I863" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J863" t="b">
+        <v>0</v>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 28.04 &lt;= Upper 29.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>PARA</t>
+        </is>
+      </c>
+      <c r="D864" t="n">
+        <v>1</v>
+      </c>
+      <c r="E864" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F864" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G864" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H864" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I864" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J864" t="b">
+        <v>0</v>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 1.06 &lt;= EMA21 1.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>525.75</v>
+      </c>
+      <c r="E865" t="n">
+        <v>567.67</v>
+      </c>
+      <c r="F865" t="n">
+        <v>567.67</v>
+      </c>
+      <c r="G865" t="n">
+        <v>532.9400000000001</v>
+      </c>
+      <c r="H865" t="n">
+        <v>528.98</v>
+      </c>
+      <c r="I865" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J865" t="b">
+        <v>0</v>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 525.75 &lt;= Upper 567.67)</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>TME</t>
+        </is>
+      </c>
+      <c r="D866" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="E866" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="F866" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="G866" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="H866" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="I866" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J866" t="b">
+        <v>0</v>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 8.15 &lt;= EMA21 8.44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="E867" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="F867" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="G867" t="n">
+        <v>106.39</v>
+      </c>
+      <c r="H867" t="n">
+        <v>107.43</v>
+      </c>
+      <c r="I867" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J867" t="b">
+        <v>0</v>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 106.39 &lt;= EMA21 107.43)</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="D868" t="n">
+        <v>904.77</v>
+      </c>
+      <c r="E868" t="n">
+        <v>981.22</v>
+      </c>
+      <c r="F868" t="n">
+        <v>981.22</v>
+      </c>
+      <c r="G868" t="n">
+        <v>917.0599999999999</v>
+      </c>
+      <c r="H868" t="n">
+        <v>930.58</v>
+      </c>
+      <c r="I868" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J868" t="b">
+        <v>0</v>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 917.06 &lt;= EMA21 930.58)</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D869" t="n">
+        <v>155.83</v>
+      </c>
+      <c r="E869" t="n">
+        <v>170.74</v>
+      </c>
+      <c r="F869" t="n">
+        <v>170.74</v>
+      </c>
+      <c r="G869" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="H869" t="n">
+        <v>158.44</v>
+      </c>
+      <c r="I869" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J869" t="b">
+        <v>0</v>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 155.83 &lt;= Upper 170.74)</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="D870" t="n">
+        <v>308.74</v>
+      </c>
+      <c r="E870" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="F870" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="G870" t="n">
+        <v>315.12</v>
+      </c>
+      <c r="H870" t="n">
+        <v>323.12</v>
+      </c>
+      <c r="I870" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J870" t="b">
+        <v>0</v>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 315.12 &lt;= EMA21 323.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
+        <v>196.82</v>
+      </c>
+      <c r="E871" t="n">
+        <v>224.36</v>
+      </c>
+      <c r="F871" t="n">
+        <v>224.36</v>
+      </c>
+      <c r="G871" t="n">
+        <v>201.05</v>
+      </c>
+      <c r="H871" t="n">
+        <v>205.96</v>
+      </c>
+      <c r="I871" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J871" t="b">
+        <v>0</v>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 201.05 &lt;= EMA21 205.96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D872" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="E872" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="F872" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="G872" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="H872" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="I872" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J872" t="b">
+        <v>0</v>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 58.49 &lt;= Upper 59.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D873" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="E873" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="F873" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="G873" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H873" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="I873" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J873" t="b">
+        <v>0</v>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 12.15 &lt;= EMA21 12.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="D874" t="n">
+        <v>124.58</v>
+      </c>
+      <c r="E874" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F874" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="G874" t="n">
+        <v>126.31</v>
+      </c>
+      <c r="H874" t="n">
+        <v>125.62</v>
+      </c>
+      <c r="I874" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J874" t="b">
+        <v>0</v>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 124.58 &lt;= Upper 132.88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="D875" t="n">
+        <v>118.17</v>
+      </c>
+      <c r="E875" t="n">
+        <v>138.97</v>
+      </c>
+      <c r="F875" t="n">
+        <v>138.97</v>
+      </c>
+      <c r="G875" t="n">
+        <v>124.02</v>
+      </c>
+      <c r="H875" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="I875" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J875" t="b">
+        <v>0</v>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 124.02 &lt;= EMA21 126.68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>BJ</t>
+        </is>
+      </c>
+      <c r="D876" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="E876" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="F876" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="G876" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="H876" t="n">
+        <v>92.14</v>
+      </c>
+      <c r="I876" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J876" t="b">
+        <v>0</v>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 91.14 &lt;= EMA21 92.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="D877" t="n">
+        <v>230.74</v>
+      </c>
+      <c r="E877" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="F877" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="G877" t="n">
+        <v>229.46</v>
+      </c>
+      <c r="H877" t="n">
+        <v>232.79</v>
+      </c>
+      <c r="I877" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J877" t="b">
+        <v>0</v>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 229.46 &lt;= EMA21 232.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+      <c r="D878" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="E878" t="n">
+        <v>152.99</v>
+      </c>
+      <c r="F878" t="n">
+        <v>152.99</v>
+      </c>
+      <c r="G878" t="n">
+        <v>130.05</v>
+      </c>
+      <c r="H878" t="n">
+        <v>136.47</v>
+      </c>
+      <c r="I878" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J878" t="b">
+        <v>0</v>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 130.05 &lt;= EMA21 136.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="D879" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E879" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="F879" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="G879" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="H879" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="I879" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J879" t="b">
+        <v>0</v>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 37.77 &lt;= EMA21 38.76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D880" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="E880" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="F880" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="G880" t="n">
+        <v>106.08</v>
+      </c>
+      <c r="H880" t="n">
+        <v>112.08</v>
+      </c>
+      <c r="I880" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J880" t="b">
+        <v>0</v>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 106.08 &lt;= EMA21 112.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D881" t="n">
+        <v>98.73999999999999</v>
+      </c>
+      <c r="E881" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="F881" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="G881" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="H881" t="n">
+        <v>104.08</v>
+      </c>
+      <c r="I881" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J881" t="b">
+        <v>0</v>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 102.34 &lt;= EMA21 104.08)</t>
         </is>
       </c>
     </row>
@@ -33664,7 +37892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34133,6 +38361,130 @@
         <v>2.21</v>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>84.37</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="E17" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>567.29</v>
+      </c>
+      <c r="E18" t="n">
+        <v>541.76</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>QUEUED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="E19" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>QUEUED</t>
         </is>
@@ -34149,7 +38501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34230,19 +38582,19 @@
         <v>1961.07</v>
       </c>
       <c r="F2" t="n">
-        <v>653.6900000000001</v>
+        <v>648.03</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="H2" t="n">
-        <v>624.27</v>
+        <v>634.35</v>
       </c>
       <c r="I2" t="n">
-        <v>653.6900000000001</v>
+        <v>664.239990234375</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -34368,6 +38720,47 @@
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>56</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1986.88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -34771,7 +39164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35561,6 +39954,55 @@
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:45:33</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>35583981F4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>56</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Entry Breakout</t>
         </is>
@@ -35577,7 +40019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35685,6 +40127,33 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>Opened at 104.36 below SL of 109.14. Filled at Open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:45:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SKIPPED_CAPITAL_EXHAUSTED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Qualified breakout on DELL skipped: all slots full or insufficient cash.</t>
         </is>
       </c>
     </row>
@@ -35699,7 +40168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36145,6 +40614,39 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>04:45:34</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9736.440000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9761.879999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-238.12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
